--- a/temp/WRCF End-to-End Test Cases_reverified-v2.xlsx
+++ b/temp/WRCF End-to-End Test Cases_reverified-v2.xlsx
@@ -1051,7 +1051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y18"/>
+  <dimension ref="A1:Z18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="29.140625" defaultRowHeight="15"/>
   <cols>
     <col width="11.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1073,6 +1073,8 @@
     <col width="22" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
     <col width="28" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1201,6 +1203,11 @@
           <t>Test run @ 08:17 PM @ 02/04/26</t>
         </is>
       </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Test run @ 11:11 PM @ 03/04/26</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="30.75" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
@@ -1300,7 +1307,7 @@
       </c>
       <c r="T2" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -1324,6 +1331,11 @@
         </is>
       </c>
       <c r="Y2" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -1427,7 +1439,7 @@
       </c>
       <c r="T3" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -1451,6 +1463,11 @@
         </is>
       </c>
       <c r="Y3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -1554,7 +1571,7 @@
       </c>
       <c r="T4" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1578,6 +1595,11 @@
         </is>
       </c>
       <c r="Y4" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -1681,7 +1703,7 @@
       </c>
       <c r="T5" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1705,6 +1727,11 @@
         </is>
       </c>
       <c r="Y5" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -1808,7 +1835,7 @@
       </c>
       <c r="T6" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: No deterministic existing task row is available under the selected skill for duplicate validation.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: No deterministic existing task row is available under the selected skill for duplicate validation.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1834,6 +1861,11 @@
       <c r="Y6" t="inlineStr">
         <is>
           <t>failed: no deterministic existing task row is available under the selected...</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>failed: No deterministic existing task row is available under the selected skill for duplicate val</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1967,7 @@
       </c>
       <c r="T7" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: No deterministic existing task row is available under the selected skill for duplicate validation.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: No deterministic existing task row is available under the selected skill for duplicate validation.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1961,6 +1993,11 @@
       <c r="Y7" t="inlineStr">
         <is>
           <t>failed: no deterministic existing task row is available under the selected...</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>failed: No deterministic existing task row is available under the selected skill for duplicate val</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2099,7 @@
       </c>
       <c r="T8" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: expect(locator).toHaveCount(expected) failed</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: expect(locator).toHaveCount(expected) failed</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -2086,6 +2123,11 @@
         </is>
       </c>
       <c r="Y8" t="inlineStr">
+        <is>
+          <t>failed: expect(locator).toHaveCount(expected) failed</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>failed: expect(locator).toHaveCount(expected) failed</t>
         </is>
@@ -2189,7 +2231,7 @@
       </c>
       <c r="T9" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: No deterministic existing task row is available under the selected skill for edit/delete coverage.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: No deterministic existing task row is available under the selected skill for edit/delete coverage.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -2215,6 +2257,11 @@
       <c r="Y9" t="inlineStr">
         <is>
           <t>failed: no deterministic existing task row is available under the selected...</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>failed: No deterministic existing task row is available under the selected skill for edit/delete c</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2363,7 @@
       </c>
       <c r="T10" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: No deterministic existing task row is available under the selected skill for edit/delete coverage.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: No deterministic existing task row is available under the selected skill for edit/delete coverage.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -2342,6 +2389,11 @@
       <c r="Y10" t="inlineStr">
         <is>
           <t>failed: no deterministic existing task row is available under the selected...</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>failed: No deterministic existing task row is available under the selected skill for edit/delete c</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2495,7 @@
       </c>
       <c r="T11" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: No deterministic existing task row is available under the selected skill for edit/delete coverage.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: No deterministic existing task row is available under the selected skill for edit/delete coverage.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -2469,6 +2521,11 @@
       <c r="Y11" t="inlineStr">
         <is>
           <t>failed: no deterministic existing task row is available under the selected...</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>failed: No deterministic existing task row is available under the selected skill for edit/delete c</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2627,7 @@
       </c>
       <c r="T12" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: No deterministic existing task row is available under the selected skill for edit/delete coverage.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: No deterministic existing task row is available under the selected skill for edit/delete coverage.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2596,6 +2653,11 @@
       <c r="Y12" t="inlineStr">
         <is>
           <t>failed: no deterministic existing task row is available under the selected...</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>failed: No deterministic existing task row is available under the selected skill for edit/delete c</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2759,7 @@
       </c>
       <c r="T13" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2721,6 +2783,11 @@
         </is>
       </c>
       <c r="Y13" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -2824,7 +2891,7 @@
       </c>
       <c r="T14" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2848,6 +2915,11 @@
         </is>
       </c>
       <c r="Y14" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -2951,7 +3023,7 @@
       </c>
       <c r="T15" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: expect(locator).not.toBeVisible() failed</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: expect(locator).not.toBeVisible() failed</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2975,6 +3047,11 @@
         </is>
       </c>
       <c r="Y15" t="inlineStr">
+        <is>
+          <t>failed: expect(locator).not.toBeVisible() failed</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>failed: expect(locator).not.toBeVisible() failed</t>
         </is>
@@ -3069,6 +3146,11 @@
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -3159,6 +3241,11 @@
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -3247,6 +3334,11 @@
       <c r="T18" s="13" t="inlineStr">
         <is>
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>not run</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:Y16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="32.42578125" defaultRowHeight="15"/>
   <cols>
     <col width="11.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3286,6 +3378,8 @@
     <col width="22" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
     <col width="28" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -3409,6 +3503,11 @@
           <t>Test run @ 08:17 PM @ 02/04/26</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Test run @ 11:11 PM @ 03/04/26</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
@@ -3508,7 +3607,7 @@
       </c>
       <c r="T2" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -3522,6 +3621,11 @@
         </is>
       </c>
       <c r="X2" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -3625,7 +3729,7 @@
       </c>
       <c r="T3" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -3639,6 +3743,11 @@
         </is>
       </c>
       <c r="X3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -3742,7 +3851,7 @@
       </c>
       <c r="T4" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -3756,6 +3865,11 @@
         </is>
       </c>
       <c r="X4" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -3859,7 +3973,7 @@
       </c>
       <c r="T5" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -3873,6 +3987,11 @@
         </is>
       </c>
       <c r="X5" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -3976,7 +4095,7 @@
       </c>
       <c r="T6" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -3990,6 +4109,11 @@
         </is>
       </c>
       <c r="X6" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -4093,7 +4217,7 @@
       </c>
       <c r="T7" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs a deterministic existing control point row plus stable duplicate validation in the current local runtime.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a deterministic existing control point row plus stable duplicate validation in the current local runtime.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -4109,6 +4233,11 @@
       <c r="X7" t="inlineStr">
         <is>
           <t>failed: existing control point row plus stable duplicate validation in the...</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>failed: Needs a deterministic existing control point row plus stable duplicate validation in the c</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4339,7 @@
       </c>
       <c r="T8" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs a deterministic existing control point row plus stable duplicate validation for trimmed names.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a deterministic existing control point row plus stable duplicate validation for trimmed names.</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -4226,6 +4355,11 @@
       <c r="X8" t="inlineStr">
         <is>
           <t>failed: existing control point row plus stable duplicate validation for tri...</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>failed: Needs a deterministic existing control point row plus stable duplicate validation for trim</t>
         </is>
       </c>
     </row>
@@ -4322,12 +4456,12 @@
       </c>
       <c r="S9" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T9" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs a stable close-without-save path under a selected task to confirm list state remains unchanged.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a stable close-without-save path under a selected task to confirm list state remains unchanged.</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -4343,6 +4477,11 @@
       <c r="X9" t="inlineStr">
         <is>
           <t>failed: a stable close-without-save path under a selected task to confirm l...</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>failed: Needs a stable close-without-save path under a selected task to confirm list state remains</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4583,7 @@
       </c>
       <c r="T10" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs a deterministic existing control point row plus verified field parity for edit-preload coverage.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a deterministic existing control point row plus verified field parity for edit-preload coverage.</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -4460,6 +4599,11 @@
       <c r="X10" t="inlineStr">
         <is>
           <t>failed: existing control point row plus verified field parity for edit-prel...</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>failed: Needs a deterministic existing control point row plus verified field parity for edit-prelo</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4705,7 @@
       </c>
       <c r="T11" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs a deterministic existing control point row and stable update coverage under the selected task.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a deterministic existing control point row and stable update coverage under the selected task.</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -4577,6 +4721,11 @@
       <c r="X11" t="inlineStr">
         <is>
           <t>failed: existing control point row and stable update coverage under the sel...</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>failed: Needs a deterministic existing control point row and stable update coverage under the sele</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4827,7 @@
       </c>
       <c r="T12" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs a deterministic existing control point row and stable edit-panel access.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a deterministic existing control point row and stable edit-panel access.</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -4694,6 +4843,11 @@
       <c r="X12" t="inlineStr">
         <is>
           <t>failed: existing control point row and stable edit-panel access</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>failed: Needs a deterministic existing control point row and stable edit-panel access.</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4949,7 @@
       </c>
       <c r="T13" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs a deterministic childless control point row plus stable delete confirmation under the selected task.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a deterministic childless control point row plus stable delete confirmation under the selected task.</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -4811,6 +4965,11 @@
       <c r="X13" t="inlineStr">
         <is>
           <t>failed: childless control point row plus stable delete confirmation under t...</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>failed: Needs a deterministic childless control point row plus stable delete confirmation under th</t>
         </is>
       </c>
     </row>
@@ -4907,12 +5066,12 @@
       </c>
       <c r="S14" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T14" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs a dedicated boundary run because the current stable create case already overlaps with blank-KPI behavior.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a dedicated boundary run because the current stable create case already overlaps with blank-KPI behavior.</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -4928,6 +5087,11 @@
       <c r="X14" t="inlineStr">
         <is>
           <t>failed: a dedicated boundary run because the current stable create case alr...</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>failed: Needs a dedicated boundary run because the current stable create case already overlaps wit</t>
         </is>
       </c>
     </row>
@@ -5024,12 +5188,12 @@
       </c>
       <c r="S15" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>ui-structure</t>
         </is>
       </c>
       <c r="T15" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs source clarification because the UI marks Escalation Required and Evidence Type as required, but the current component model/enforcement does not fully expose their allowed values.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs source clarification because the UI marks Escalation Required and Evidence Type as required, but the current component model/enforcement does not fully ex</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -5045,6 +5209,11 @@
       <c r="X15" t="inlineStr">
         <is>
           <t>failed: source clarification because the UI marks Escalation Required and E...</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>failed: Needs source clarification because the UI marks Escalation Required and Evidence Type as r</t>
         </is>
       </c>
     </row>
@@ -5135,6 +5304,11 @@
       <c r="T16" s="13" t="inlineStr">
         <is>
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>not run</t>
         </is>
       </c>
     </row>
@@ -5150,7 +5324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:Y21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.5703125" customWidth="1" min="1" max="1"/>
@@ -5172,6 +5346,8 @@
     <col width="22" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
     <col width="28" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -5295,6 +5471,11 @@
           <t>Test run @ 11:09 PM @ 02/04/26</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Test run @ 11:11 PM @ 03/04/26</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
@@ -5394,7 +5575,7 @@
       </c>
       <c r="T2" s="13" t="inlineStr">
         <is>
-          <t>No available industry on Manage WRCF Roles currently exposes seeded department options, so the strict department-loading check fails.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: No Roles industry context produced any department options.</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -5410,6 +5591,11 @@
       <c r="X2" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>failed: No Roles industry context produced any department options.</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5697,7 @@
       </c>
       <c r="T3" s="13" t="inlineStr">
         <is>
-          <t>Needs at least two departments with different role sets so department-scoped role filtering can be compared.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs at least two departments with different role sets in the local environment so department-scoped role filtering can be compared.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -5527,6 +5713,11 @@
       <c r="X3" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>failed: Needs at least two departments with different role sets in the local environment so depart</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5819,7 @@
       </c>
       <c r="T4" s="13" t="inlineStr">
         <is>
-          <t>Current page auto-selects the first available department when an industry is loaded, so the workbook precondition cannot be reproduced as a stable default state.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current page auto-selects the first available department when an industry is loaded, so the workbook precondition cannot be reproduced as a stable default state</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -5644,6 +5835,11 @@
       <c r="X4" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>failed: Current page auto-selects the first available department when an industry is loaded, so th</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5941,7 @@
       </c>
       <c r="T5" s="13" t="inlineStr">
         <is>
-          <t>Verified again in 11:09 PM 02/04/26 focused Roles rerun: Add Role action is available after establishing department context.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -5759,6 +5955,11 @@
         </is>
       </c>
       <c r="X5" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -5862,7 +6063,7 @@
       </c>
       <c r="T6" s="13" t="inlineStr">
         <is>
-          <t>Verified again in 11:09 PM 02/04/26 focused Roles rerun: clicking Add opens the role create form.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -5876,6 +6077,11 @@
         </is>
       </c>
       <c r="X6" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -5979,7 +6185,7 @@
       </c>
       <c r="T7" s="13" t="inlineStr">
         <is>
-          <t>Latest 11:09 PM 02/04/26 focused rerun still shows live runtime blocker: POST /wrcf/roles returns id "0", so the panel closes but the created role cannot be selected deterministically.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Role save did not complete within 10s; the create/edit panel stayed open and no validation message appeared.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -5995,6 +6201,11 @@
       <c r="X7" t="inlineStr">
         <is>
           <t>failed: live POST /wrcf/roles returns id 0</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>failed: Role save did not complete within 10s; the create/edit panel stayed open and no validation</t>
         </is>
       </c>
     </row>
@@ -6086,17 +6297,17 @@
       </c>
       <c r="R8" s="11" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="S8" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T8" s="13" t="inlineStr">
         <is>
-          <t>Verified in 11:09 PM 02/04/26 focused Roles rerun: edit action is available for the selected existing role in current context.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Role save did not complete within 10s; the create/edit panel stayed open and no validation message appeared.</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -6112,6 +6323,11 @@
       <c r="X8" t="inlineStr">
         <is>
           <t>passed</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>failed: Role save did not complete within 10s; the create/edit panel stayed open and no validation</t>
         </is>
       </c>
     </row>
@@ -6213,7 +6429,7 @@
       </c>
       <c r="T9" s="13" t="inlineStr">
         <is>
-          <t>Latest 11:09 PM 02/04/26 focused rerun is still blocked by the live role-create prerequisite: POST /wrcf/roles returns id "0", so the create-backed selected-role path is not reliable.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Role save did not complete within 10s; the create/edit panel stayed open and no validation message appeared.</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -6229,6 +6445,11 @@
       <c r="X9" t="inlineStr">
         <is>
           <t>failed: create prerequisite still blocked</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>failed: Role save did not complete within 10s; the create/edit panel stayed open and no validation</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6551,7 @@
       </c>
       <c r="T10" s="13" t="inlineStr">
         <is>
-          <t>Latest 11:09 PM 02/04/26 focused rerun is still blocked by the live role-create prerequisite: POST /wrcf/roles returns id "0", so the update flow cannot be established deterministically.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Role save did not complete within 10s; the create/edit panel stayed open and no validation message appeared.</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -6346,6 +6567,11 @@
       <c r="X10" t="inlineStr">
         <is>
           <t>failed: create prerequisite still blocked</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>failed: Role save did not complete within 10s; the create/edit panel stayed open and no validation</t>
         </is>
       </c>
     </row>
@@ -6437,17 +6663,17 @@
       </c>
       <c r="R11" s="11" t="inlineStr">
         <is>
-          <t>fail</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="S11" s="11" t="inlineStr">
         <is>
-          <t>runtime/data</t>
+          <t>none</t>
         </is>
       </c>
       <c r="T11" s="13" t="inlineStr">
         <is>
-          <t>Latest 11:09 PM 02/04/26 focused rerun is still blocked by the live role-create prerequisite: POST /wrcf/roles returns id "0", so delete-panel coverage cannot be established deterministically.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -6463,6 +6689,11 @@
       <c r="X11" t="inlineStr">
         <is>
           <t>failed: create prerequisite still blocked</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>passed</t>
         </is>
       </c>
     </row>
@@ -6564,7 +6795,7 @@
       </c>
       <c r="T12" s="13" t="inlineStr">
         <is>
-          <t>Needs a deterministic role with existing capability-instance mappings plus a stable dependency-block message in the current local runtime.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a deterministic role with existing capability-instance mappings plus a stable dependency-block message in the current local runtime.</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -6580,6 +6811,11 @@
       <c r="X12" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>failed: Needs a deterministic role with existing capability-instance mappings plus a stable depend</t>
         </is>
       </c>
     </row>
@@ -6681,7 +6917,7 @@
       </c>
       <c r="T13" s="13" t="inlineStr">
         <is>
-          <t>Needs a lower-privilege Viewer or Auditor account for RBAC coverage.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a lower-privilege Viewer or Auditor account for RBAC coverage.</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -6697,6 +6933,11 @@
       <c r="X13" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>failed: Needs a lower-privilege Viewer or Auditor account for RBAC coverage.</t>
         </is>
       </c>
     </row>
@@ -6881,7 +7122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:Y18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.5703125" customWidth="1" min="1" max="1"/>
@@ -6903,6 +7144,8 @@
     <col width="22" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
     <col width="28" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -7026,6 +7269,11 @@
           <t>Test run @ 11:09 PM @ 02/04/26</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Test run @ 11:11 PM @ 03/04/26</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
@@ -7125,7 +7373,7 @@
       </c>
       <c r="T2" s="13" t="inlineStr">
         <is>
-          <t>Latest 11:09 PM 02/04/26 focused rerun still cannot establish a deterministic selected-role prerequisite because live POST /wrcf/roles returns id "0".</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Role-scoped hierarchy now waits for explicit role selection, but the current local runtime still blocks role creation/save, so the selected-role prerequisite ca</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -7141,6 +7389,11 @@
       <c r="X2" t="inlineStr">
         <is>
           <t>failed: selected-role prerequisite blocked</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>failed: Role-scoped hierarchy now waits for explicit role selection, but the current local runtime</t>
         </is>
       </c>
     </row>
@@ -7242,7 +7495,7 @@
       </c>
       <c r="T3" s="13" t="inlineStr">
         <is>
-          <t>Verified again in 11:09 PM 02/04/26 focused rerun: without a selected role, the Mappings action remains unavailable.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -7256,6 +7509,11 @@
         </is>
       </c>
       <c r="X3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -7359,7 +7617,7 @@
       </c>
       <c r="T4" s="13" t="inlineStr">
         <is>
-          <t>Latest 11:09 PM 02/04/26 focused rerun still cannot validate role-scoped mapping restriction because live POST /wrcf/roles returns id "0" and blocks deterministic role selection.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a working selected-role path first; current local runtime still blocks role creation/save before role-scoped mapping restriction can be validated.</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -7375,6 +7633,11 @@
       <c r="X4" t="inlineStr">
         <is>
           <t>failed: selected-role prerequisite blocked</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>failed: Needs a working selected-role path first; current local runtime still blocks role creation</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7739,7 @@
       </c>
       <c r="T5" s="13" t="inlineStr">
         <is>
-          <t>The dialog groups pending mappings by PWO, but a deterministic selected role plus pending role-mapping entries are required before the grouping scenario can be executed.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: The dialog groups pending mappings by PWO, but a deterministic selected role plus pending role-mapping entries are required before the workbook grouping scenari</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -7492,6 +7755,11 @@
       <c r="X5" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">failed: The dialog groups pending mappings by PWO, but a deterministic selected role plus pending </t>
         </is>
       </c>
     </row>
@@ -7593,7 +7861,7 @@
       </c>
       <c r="T6" s="13" t="inlineStr">
         <is>
-          <t>Needs a deterministic seeded role with existing saved role-capability-instance mappings in the current local environment.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a deterministic seeded role with existing saved role-capability-instance mappings in the current local environment.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -7609,6 +7877,11 @@
       <c r="X6" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>failed: Needs a deterministic seeded role with existing saved role-capability-instance mappings in</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7983,7 @@
       </c>
       <c r="T7" s="13" t="inlineStr">
         <is>
-          <t>Needs a deterministic selected role plus an unmapped capability-instance row; current runtime blocks role creation/selection before pending mapping can be staged.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a deterministic selected role plus an unmapped capability-instance row; current runtime blocks role creation/selection before pending mapping can be stage</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -7726,6 +7999,11 @@
       <c r="X7" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>failed: Needs a deterministic selected role plus an unmapped capability-instance row; current runt</t>
         </is>
       </c>
     </row>
@@ -7827,7 +8105,7 @@
       </c>
       <c r="T8" s="13" t="inlineStr">
         <is>
-          <t>Needs a deterministic selected role plus pending mapping rows; current runtime blocks role creation/selection before save coverage can be exercised.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a deterministic selected role plus pending mapping rows; current runtime blocks role creation/selection before save coverage can be exercised.</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -7843,6 +8121,11 @@
       <c r="X8" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>failed: Needs a deterministic selected role plus pending mapping rows; current runtime blocks role</t>
         </is>
       </c>
     </row>
@@ -7944,7 +8227,7 @@
       </c>
       <c r="T9" s="13" t="inlineStr">
         <is>
-          <t>Needs a stable end-to-end role mapping save path plus seeded role data for reopen verification.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a stable end-to-end role mapping save path plus seeded role data for reopen verification.</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -7960,6 +8243,11 @@
       <c r="X9" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>failed: Needs a stable end-to-end role mapping save path plus seeded role data for reopen verifica</t>
         </is>
       </c>
     </row>
@@ -8061,7 +8349,7 @@
       </c>
       <c r="T10" s="13" t="inlineStr">
         <is>
-          <t>Needs a deterministic selected role with existing saved mappings so a mapped row can be opened and removed.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a deterministic selected role with existing saved mappings so a mapped row can be opened and removed.</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -8077,6 +8365,11 @@
       <c r="X10" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>failed: Needs a deterministic selected role with existing saved mappings so a mapped row can be op</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8471,7 @@
       </c>
       <c r="T11" s="13" t="inlineStr">
         <is>
-          <t>Needs a deterministic selected role with an existing saved mapping and a working remove-plus-save flow.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a deterministic selected role with an existing saved mapping and a working remove-plus-save flow.</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -8194,6 +8487,11 @@
       <c r="X11" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>failed: Needs a deterministic selected role with an existing saved mapping and a working remove-pl</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8593,7 @@
       </c>
       <c r="T12" s="13" t="inlineStr">
         <is>
-          <t>Needs a deterministic selected role with an already-saved mapping plus a stable re-add path to confirm duplicate prevention.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a deterministic selected role with an already-saved mapping plus a stable re-add path to confirm duplicate prevention.</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -8311,6 +8609,11 @@
       <c r="X12" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>failed: Needs a deterministic selected role with an already-saved mapping plus a stable re-add pat</t>
         </is>
       </c>
     </row>
@@ -8412,7 +8715,7 @@
       </c>
       <c r="T13" s="13" t="inlineStr">
         <is>
-          <t>Needs a deterministic selected role plus controlled capability-instance seed data to compare instantiated versus non-instantiated combinations.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a deterministic selected role plus controlled capability-instance seed data to compare instantiated versus non-instantiated combinations.</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -8428,6 +8731,11 @@
       <c r="X13" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>failed: Needs a deterministic selected role plus controlled capability-instance seed data to compa</t>
         </is>
       </c>
     </row>
@@ -8529,7 +8837,7 @@
       </c>
       <c r="T14" s="13" t="inlineStr">
         <is>
-          <t>Needs a working saved role-mapping create path plus a way to inspect the persisted mandatory flag after save.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a working saved role-mapping create path plus a way to inspect the persisted mandatory flag after save.</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -8545,6 +8853,11 @@
       <c r="X14" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>failed: Needs a working saved role-mapping create path plus a way to inspect the persisted mandato</t>
         </is>
       </c>
     </row>
@@ -8646,7 +8959,7 @@
       </c>
       <c r="T15" s="13" t="inlineStr">
         <is>
-          <t>Needs a working saved role-mapping create path plus a way to inspect the persisted weight value after save.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a working saved role-mapping create path plus a way to inspect the persisted weight value after save.</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -8662,6 +8975,11 @@
       <c r="X15" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">failed: Needs a working saved role-mapping create path plus a way to inspect the persisted weight </t>
         </is>
       </c>
     </row>
@@ -8763,7 +9081,7 @@
       </c>
       <c r="T16" s="13" t="inlineStr">
         <is>
-          <t>Needs a lower-privilege Viewer or Auditor account for RBAC mapping coverage.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a lower-privilege Viewer or Auditor account for RBAC mapping coverage.</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -8779,6 +9097,11 @@
       <c r="X16" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>failed: Needs a lower-privilege Viewer or Auditor account for RBAC mapping coverage.</t>
         </is>
       </c>
     </row>
@@ -8837,7 +9160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.5703125" customWidth="1" min="1" max="1"/>
@@ -8853,11 +9176,14 @@
     <col width="26" customWidth="1" min="13" max="13"/>
     <col width="27.28515625" customWidth="1" min="14" max="14"/>
     <col hidden="1" width="12" customWidth="1" min="15" max="16"/>
+    <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
     <col hidden="1" width="16" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
     <col width="28" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -8971,6 +9297,11 @@
           <t>Test run @ 03:22 PM @ 03/04/26</t>
         </is>
       </c>
+      <c r="W1" s="26" t="inlineStr">
+        <is>
+          <t>Test run @ 11:11 PM @ 03/04/26</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
@@ -9070,12 +9401,17 @@
       </c>
       <c r="T2" s="13" t="inlineStr">
         <is>
-          <t>Revalidated on 03/04/26: live UI at /manage-company is a CRUD page and does not expose the company WRCF dashboard/template-linked landing surface described in the workbook.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live UI at /manage-company is a CRUD management page and does not expose the company WRCF dashboard/template-linked landing surface described in the wor</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>failed: company WRCF dashboard surface missing</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>failed: Current live UI at /manage-company is a CRUD management page and does not expose the compa</t>
         </is>
       </c>
     </row>
@@ -9177,12 +9513,17 @@
       </c>
       <c r="T3" s="13" t="inlineStr">
         <is>
-          <t>Revalidated on 03/04/26: live Manage Company page does not expose a company-WRCF version summary area with Industry Version, Company Version, or Overrides count.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose a company-WRCF version summary area with Industry Version, Company Version, or Overrides count.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>failed: version summary surface missing</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">failed: Current live Manage Company page does not expose a company-WRCF version summary area with </t>
         </is>
       </c>
     </row>
@@ -9284,12 +9625,17 @@
       </c>
       <c r="T4" s="13" t="inlineStr">
         <is>
-          <t>Revalidated on 03/04/26: live Manage Company page does not expose company-WRCF override sections or upgrade state sections.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose company-WRCF override sections or upgrade state sections.</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>failed: override and upgrade sections missing</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>failed: Current live Manage Company page does not expose company-WRCF override sections or upgrade</t>
         </is>
       </c>
     </row>
@@ -9386,17 +9732,22 @@
       </c>
       <c r="S5" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T5" s="13" t="inlineStr">
         <is>
-          <t>Companies Playwright spec now exists; this workbook row was not rerun in the 03:22 PM 03/04/26 batch.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: This workbook permission case depends on a company-WRCF override surface and a dedicated Company Admin account matrix that are not represented in the current li</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>failed: This workbook permission case depends on a company-WRCF override surface and a dedicated C</t>
         </is>
       </c>
     </row>
@@ -9493,17 +9844,22 @@
       </c>
       <c r="S6" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T6" s="13" t="inlineStr">
         <is>
-          <t>Companies Playwright spec now exists; this workbook row was not rerun in the 03:22 PM 03/04/26 batch.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: This workbook permission case targets industry-master WRCF flows rather than the current Manage Company CRUD page and needs dedicated RBAC accounts to verify.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>failed: This workbook permission case targets industry-master WRCF flows rather than the current M</t>
         </is>
       </c>
     </row>
@@ -9600,17 +9956,22 @@
       </c>
       <c r="S7" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>product-gap</t>
         </is>
       </c>
       <c r="T7" s="13" t="inlineStr">
         <is>
-          <t>Companies Playwright spec now exists; this workbook row was not rerun in the 03:22 PM 03/04/26 batch.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose the company-WRCF export surface and this role-based case needs a dedicated Auditor account.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">failed: Current live Manage Company page does not expose the company-WRCF export surface and this </t>
         </is>
       </c>
     </row>
@@ -9707,17 +10068,22 @@
       </c>
       <c r="S8" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>product-gap</t>
         </is>
       </c>
       <c r="T8" s="13" t="inlineStr">
         <is>
-          <t>Companies Playwright spec now exists; this workbook row was not rerun in the 03:22 PM 03/04/26 batch.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live runtime does not expose the company role requirement view described in the workbook and this case needs an Employee account.</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>failed: Current live runtime does not expose the company role requirement view described in the wo</t>
         </is>
       </c>
     </row>
@@ -9814,17 +10180,22 @@
       </c>
       <c r="S9" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>product-gap</t>
         </is>
       </c>
       <c r="T9" s="13" t="inlineStr">
         <is>
-          <t>Companies Playwright spec now exists; this workbook row was not rerun in the 03:22 PM 03/04/26 batch.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose company-specific capability-instance override editing or the hybrid master-plus-override save flow.</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>failed: Current live Manage Company page does not expose company-specific capability-instance over</t>
         </is>
       </c>
     </row>
@@ -9921,17 +10292,22 @@
       </c>
       <c r="S10" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>product-gap</t>
         </is>
       </c>
       <c r="T10" s="13" t="inlineStr">
         <is>
-          <t>Companies Playwright spec now exists; this workbook row was not rerun in the 03:22 PM 03/04/26 batch.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose the final merged company-WRCF runtime view described in the workbook.</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>failed: Current live Manage Company page does not expose the final merged company-WRCF runtime vie</t>
         </is>
       </c>
     </row>
@@ -10028,17 +10404,22 @@
       </c>
       <c r="S11" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>product-gap</t>
         </is>
       </c>
       <c r="T11" s="13" t="inlineStr">
         <is>
-          <t>Companies Playwright spec now exists; this workbook row was not rerun in the 03:22 PM 03/04/26 batch.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose Company Role Adjustments or Industry Role Template vs Company Role Variant comparison.</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>failed: Current live Manage Company page does not expose Company Role Adjustments or Industry Role</t>
         </is>
       </c>
     </row>
@@ -10135,17 +10516,22 @@
       </c>
       <c r="S12" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>product-gap</t>
         </is>
       </c>
       <c r="T12" s="13" t="inlineStr">
         <is>
-          <t>Companies Playwright spec now exists; this workbook row was not rerun in the 03:22 PM 03/04/26 batch.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose the workbook role-comparison screen needed for this color-coding validation.</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>failed: Current live Manage Company page does not expose the workbook role-comparison screen neede</t>
         </is>
       </c>
     </row>
@@ -10242,17 +10628,22 @@
       </c>
       <c r="S13" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>product-gap</t>
         </is>
       </c>
       <c r="T13" s="13" t="inlineStr">
         <is>
-          <t>Companies Playwright spec now exists; this workbook row was not rerun in the 03:22 PM 03/04/26 batch.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose the company role-variant creation surface described in the workbook.</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>failed: Current live Manage Company page does not expose the company role-variant creation surface</t>
         </is>
       </c>
     </row>
@@ -10349,17 +10740,22 @@
       </c>
       <c r="S14" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>product-gap</t>
         </is>
       </c>
       <c r="T14" s="13" t="inlineStr">
         <is>
-          <t>Companies Playwright spec now exists; this workbook row was not rerun in the 03:22 PM 03/04/26 batch.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose company role-variant capability weight adjustment.</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>failed: Current live Manage Company page does not expose company role-variant capability weight ad</t>
         </is>
       </c>
     </row>
@@ -10456,17 +10852,22 @@
       </c>
       <c r="S15" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>product-gap</t>
         </is>
       </c>
       <c r="T15" s="13" t="inlineStr">
         <is>
-          <t>Companies Playwright spec now exists; this workbook row was not rerun in the 03:22 PM 03/04/26 batch.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose company role-variant certification-threshold override editing.</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>failed: Current live Manage Company page does not expose company role-variant certification-thresh</t>
         </is>
       </c>
     </row>
@@ -10563,17 +10964,22 @@
       </c>
       <c r="S16" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>product-gap</t>
         </is>
       </c>
       <c r="T16" s="13" t="inlineStr">
         <is>
-          <t>Companies Playwright spec now exists; this workbook row was not rerun in the 03:22 PM 03/04/26 batch.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose industry/company WRCF version comparison or Upgrade Available state.</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">failed: Current live Manage Company page does not expose industry/company WRCF version comparison </t>
         </is>
       </c>
     </row>
@@ -10670,17 +11076,22 @@
       </c>
       <c r="S17" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>product-gap</t>
         </is>
       </c>
       <c r="T17" s="13" t="inlineStr">
         <is>
-          <t>Companies Playwright spec now exists; this workbook row was not rerun in the 03:22 PM 03/04/26 batch.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose the workbook Upgrade &amp; Merge diff flow.</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>failed: Current live Manage Company page does not expose the workbook Upgrade &amp; Merge diff flow.</t>
         </is>
       </c>
     </row>
@@ -10777,17 +11188,22 @@
       </c>
       <c r="S18" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>product-gap</t>
         </is>
       </c>
       <c r="T18" s="13" t="inlineStr">
         <is>
-          <t>Companies Playwright spec now exists; this workbook row was not rerun in the 03:22 PM 03/04/26 batch.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose the workbook Upgrade &amp; Merge accept-all flow or company version generation.</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>failed: Current live Manage Company page does not expose the workbook Upgrade &amp; Merge accept-all f</t>
         </is>
       </c>
     </row>
@@ -10884,17 +11300,22 @@
       </c>
       <c r="S19" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>product-gap</t>
         </is>
       </c>
       <c r="T19" s="13" t="inlineStr">
         <is>
-          <t>Companies Playwright spec now exists; this workbook row was not rerun in the 03:22 PM 03/04/26 batch.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose the workbook selective upgrade-merge decision flow.</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>failed: Current live Manage Company page does not expose the workbook selective upgrade-merge deci</t>
         </is>
       </c>
     </row>
@@ -10991,17 +11412,22 @@
       </c>
       <c r="S20" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>product-gap</t>
         </is>
       </c>
       <c r="T20" s="13" t="inlineStr">
         <is>
-          <t>Companies Playwright spec now exists; this workbook row was not rerun in the 03:22 PM 03/04/26 batch.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose the workbook Defer Upgrade flow or company-WRCF version state.</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>failed: Current live Manage Company page does not expose the workbook Defer Upgrade flow or compan</t>
         </is>
       </c>
     </row>
@@ -11060,7 +11486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:W16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.5703125" customWidth="1" min="1" max="1"/>
@@ -11076,11 +11502,14 @@
     <col width="26" customWidth="1" min="13" max="13"/>
     <col width="27.28515625" customWidth="1" min="14" max="14"/>
     <col hidden="1" width="12" customWidth="1" min="15" max="16"/>
+    <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
     <col hidden="1" width="16" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
     <col width="28" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -11194,6 +11623,11 @@
           <t>Test run @ 03:22 PM @ 03/04/26</t>
         </is>
       </c>
+      <c r="W1" s="26" t="inlineStr">
+        <is>
+          <t>Test run @ 11:11 PM @ 03/04/26</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
@@ -11266,9 +11700,6 @@
           <t>Admin user</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>fail</t>
@@ -11276,17 +11707,22 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>not-generated</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Seeded from College Student Onbaording FS.pdf on 03/04/26; Playwright spec not generated yet.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for created college to appear in Manage College list</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>failed: Waiting for created college to appear in Manage College list</t>
         </is>
       </c>
     </row>
@@ -11361,9 +11797,6 @@
           <t>College dataset</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>fail</t>
@@ -11371,17 +11804,22 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>not-generated</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Seeded from College Student Onbaording FS.pdf on 03/04/26; Playwright spec not generated yet.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for created college to appear in Manage College list</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>failed: Waiting for created college to appear in Manage College list</t>
         </is>
       </c>
     </row>
@@ -11456,9 +11894,6 @@
           <t>College dataset</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>fail</t>
@@ -11466,17 +11901,22 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>not-generated</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Seeded from College Student Onbaording FS.pdf on 03/04/26; Playwright spec not generated yet.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for created college to appear in Manage College list</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>failed: Waiting for created college to appear in Manage College list</t>
         </is>
       </c>
     </row>
@@ -11551,9 +11991,6 @@
           <t>College list</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>fail</t>
@@ -11561,17 +11998,22 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>not-generated</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Seeded from College Student Onbaording FS.pdf on 03/04/26; Playwright spec not generated yet.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for created college to appear in Manage College list</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>failed: Waiting for created college to appear in Manage College list</t>
         </is>
       </c>
     </row>
@@ -11646,9 +12088,6 @@
           <t>College detail content</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>fail</t>
@@ -11656,17 +12095,22 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>not-generated</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Seeded from College Student Onbaording FS.pdf on 03/04/26; Playwright spec not generated yet.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: This case needs a deterministic college record with long description content so the collapse/expand control is guaranteed to render in the live runtime.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>failed: This case needs a deterministic college record with long description content so the collap</t>
         </is>
       </c>
     </row>
@@ -11741,27 +12185,29 @@
           <t>Admin user</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>fail</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>not-generated</t>
+          <t>none</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Seeded from College Student Onbaording FS.pdf on 03/04/26; Playwright spec not generated yet.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>passed</t>
         </is>
       </c>
     </row>
@@ -11836,9 +12282,6 @@
           <t>Existing college</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>fail</t>
@@ -11846,17 +12289,22 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>not-generated</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Seeded from College Student Onbaording FS.pdf on 03/04/26; Playwright spec not generated yet.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for created college to appear in Manage College list</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>failed: Waiting for created college to appear in Manage College list</t>
         </is>
       </c>
     </row>
@@ -11931,27 +12379,29 @@
           <t>College form</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>fail</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>not-generated</t>
+          <t>none</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Seeded from College Student Onbaording FS.pdf on 03/04/26; Playwright spec not generated yet.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>passed</t>
         </is>
       </c>
     </row>
@@ -12026,9 +12476,6 @@
           <t>College form</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>fail</t>
@@ -12036,17 +12483,22 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>not-generated</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Seeded from College Student Onbaording FS.pdf on 03/04/26; Playwright spec not generated yet.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for created college to appear in Manage College list</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>failed: Waiting for created college to appear in Manage College list</t>
         </is>
       </c>
     </row>
@@ -12121,9 +12573,6 @@
           <t>College form</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>fail</t>
@@ -12131,17 +12580,22 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>not-generated</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Seeded from College Student Onbaording FS.pdf on 03/04/26; Playwright spec not generated yet.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: expect(locator).toBeEnabled() failed</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>failed: expect(locator).toBeEnabled() failed</t>
         </is>
       </c>
     </row>
@@ -12216,9 +12670,6 @@
           <t>Clubs master data</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>fail</t>
@@ -12226,17 +12677,22 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>not-generated</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Seeded from College Student Onbaording FS.pdf on 03/04/26; Playwright spec not generated yet.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Live Manage College form exposes Local Club Chapters, but this workbook case needs a deterministic save-safe college record to verify persisted club linkage.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>failed: Live Manage College form exposes Local Club Chapters, but this workbook case needs a deter</t>
         </is>
       </c>
     </row>
@@ -12311,9 +12767,6 @@
           <t>Users master data</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>fail</t>
@@ -12321,17 +12774,22 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>not-generated</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Seeded from College Student Onbaording FS.pdf on 03/04/26; Playwright spec not generated yet.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Live Manage College form exposes key-contact selectors, but this workbook case needs a deterministic save-safe college record to verify persisted contact mappin</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>failed: Live Manage College form exposes key-contact selectors, but this workbook case needs a det</t>
         </is>
       </c>
     </row>
@@ -12406,9 +12864,6 @@
           <t>College admin</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>fail</t>
@@ -12416,17 +12871,22 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>not-generated</t>
+          <t>product-gap</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Seeded from College Student Onbaording FS.pdf on 03/04/26; Playwright spec not generated yet.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: College Student Onboarding is described in the FS, but the current live admin runtime does not expose a separate student-onboarding page under Manage College.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>failed: College Student Onboarding is described in the FS, but the current live admin runtime does</t>
         </is>
       </c>
     </row>
@@ -12501,9 +12961,6 @@
           <t>Bulk template + student data</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>fail</t>
@@ -12511,17 +12968,22 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>not-generated</t>
+          <t>product-gap</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Seeded from College Student Onbaording FS.pdf on 03/04/26; Playwright spec not generated yet.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Bulk student onboarding flow is documented in the FS, but the current live admin runtime does not expose that student-onboarding upload surface.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>failed: Bulk student onboarding flow is documented in the FS, but the current live admin runtime d</t>
         </is>
       </c>
     </row>
@@ -12596,9 +13058,6 @@
           <t>Student dataset</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>fail</t>
@@ -12606,17 +13065,22 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>not-generated</t>
+          <t>product-gap</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>Seeded from College Student Onbaording FS.pdf on 03/04/26; Playwright spec not generated yet.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Student management table actions are documented in the FS, but the current live admin runtime does not expose the student-onboarding management screen.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>not run</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>failed: Student management table actions are documented in the FS, but the current live admin runt</t>
         </is>
       </c>
     </row>
@@ -12844,9 +13308,6 @@
           <t>Company HR</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>fail</t>
@@ -12939,9 +13400,6 @@
           <t>Company HR</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>fail</t>
@@ -13034,9 +13492,6 @@
           <t>Internship form</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>fail</t>
@@ -13129,9 +13584,6 @@
           <t>Company/Industry roles</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>fail</t>
@@ -13224,9 +13676,6 @@
           <t>Internship entity</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>fail</t>
@@ -13319,9 +13768,6 @@
           <t>Screening configuration</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>fail</t>
@@ -13414,9 +13860,6 @@
           <t>Candidate dataset</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>fail</t>
@@ -13509,9 +13952,6 @@
           <t>Assessment engine</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>fail</t>
@@ -13604,9 +14044,6 @@
           <t>Interview data</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>fail</t>
@@ -13699,9 +14136,6 @@
           <t>Assessment + interview results</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>fail</t>
@@ -13794,9 +14228,6 @@
           <t>Selection workflow</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>fail</t>
@@ -13889,9 +14320,6 @@
           <t>Selected candidate</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>fail</t>
@@ -13984,9 +14412,6 @@
           <t>Role + WRCF data</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>fail</t>
@@ -14079,9 +14504,6 @@
           <t>Role capability instances</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>fail</t>
@@ -14174,9 +14596,6 @@
           <t>Student + mentor workflow</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>fail</t>
@@ -14269,9 +14688,6 @@
           <t>Execution tracking</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>fail</t>
@@ -14364,9 +14780,6 @@
           <t>Execution records</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>fail</t>
@@ -14459,9 +14872,6 @@
           <t>Internship execution</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>fail</t>
@@ -14554,9 +14964,6 @@
           <t>Completed internship</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>fail</t>
@@ -14592,7 +14999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X43"/>
+  <dimension ref="A1:Y43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="20.5703125" defaultRowHeight="15"/>
   <cols>
     <col width="13.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -14607,11 +15014,14 @@
     <col width="20.28515625" bestFit="1" customWidth="1" min="11" max="11"/>
     <col width="16.85546875" bestFit="1" customWidth="1" min="12" max="12"/>
     <col hidden="1" width="12" customWidth="1" min="15" max="16"/>
+    <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
     <col hidden="1" width="14" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
     <col width="28" customWidth="1" min="21" max="22"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1" thickBot="1">
@@ -14735,6 +15145,11 @@
           <t>Test run @ 09:45 PM @ 02/04/26</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Test run @ 11:11 PM @ 03/04/26</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="45" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -14834,7 +15249,7 @@
       </c>
       <c r="T2" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 09:45 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -14853,6 +15268,11 @@
         </is>
       </c>
       <c r="X2" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -14956,7 +15376,7 @@
       </c>
       <c r="T3" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 09:45 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -14975,6 +15395,11 @@
         </is>
       </c>
       <c r="X3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -15078,7 +15503,7 @@
       </c>
       <c r="T4" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 09:45 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -15097,6 +15522,11 @@
         </is>
       </c>
       <c r="X4" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -15200,7 +15630,7 @@
       </c>
       <c r="T5" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 09:45 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -15219,6 +15649,11 @@
         </is>
       </c>
       <c r="X5" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -15322,7 +15757,7 @@
       </c>
       <c r="T6" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 09:45 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -15341,6 +15776,11 @@
         </is>
       </c>
       <c r="X6" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -15444,7 +15884,7 @@
       </c>
       <c r="T7" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 09:45 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -15463,6 +15903,11 @@
         </is>
       </c>
       <c r="X7" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -15566,7 +16011,7 @@
       </c>
       <c r="T8" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: expect(received).not.toContain(expected) // indexOf</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: expect(received).not.toContain(expected) // indexOf</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -15585,6 +16030,11 @@
         </is>
       </c>
       <c r="X8" t="inlineStr">
+        <is>
+          <t>failed: expect(received).not.toContain(expected) // indexOf</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>failed: expect(received).not.toContain(expected) // indexOf</t>
         </is>
@@ -15688,7 +16138,7 @@
       </c>
       <c r="T9" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: expect(received).not.toContain(expected) // indexOf</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: expect(received).not.toContain(expected) // indexOf</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -15707,6 +16157,11 @@
         </is>
       </c>
       <c r="X9" t="inlineStr">
+        <is>
+          <t>failed: expect(received).not.toContain(expected) // indexOf</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
         <is>
           <t>failed: expect(received).not.toContain(expected) // indexOf</t>
         </is>
@@ -15810,7 +16265,7 @@
       </c>
       <c r="T10" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 09:45 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -15829,6 +16284,11 @@
         </is>
       </c>
       <c r="X10" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -15932,7 +16392,7 @@
       </c>
       <c r="T11" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: expect(locator).toContainText(expected) failed</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: expect(locator).toContainText(expected) failed</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -15951,6 +16411,11 @@
         </is>
       </c>
       <c r="X11" t="inlineStr">
+        <is>
+          <t>failed: expect(locator).toContainText(expected) failed</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>failed: expect(locator).toContainText(expected) failed</t>
         </is>
@@ -16054,7 +16519,7 @@
       </c>
       <c r="T12" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 09:45 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -16073,6 +16538,11 @@
         </is>
       </c>
       <c r="X12" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -16176,7 +16646,7 @@
       </c>
       <c r="T13" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: expect(locator).toContainText(expected) failed</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: expect(locator).toContainText(expected) failed</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -16195,6 +16665,11 @@
         </is>
       </c>
       <c r="X13" t="inlineStr">
+        <is>
+          <t>failed: expect(locator).toContainText(expected) failed</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>failed: expect(locator).toContainText(expected) failed</t>
         </is>
@@ -16298,7 +16773,7 @@
       </c>
       <c r="T14" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: expect(locator).toBeVisible() failed</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: expect(locator).toBeVisible() failed</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -16317,6 +16792,11 @@
         </is>
       </c>
       <c r="X14" t="inlineStr">
+        <is>
+          <t>failed: expect(locator).toBeVisible() failed</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
         <is>
           <t>failed: expect(locator).toBeVisible() failed</t>
         </is>
@@ -16420,7 +16900,7 @@
       </c>
       <c r="T15" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 09:45 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -16439,6 +16919,11 @@
         </is>
       </c>
       <c r="X15" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -16542,7 +17027,7 @@
       </c>
       <c r="T16" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 09:45 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -16561,6 +17046,11 @@
         </is>
       </c>
       <c r="X16" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -16664,7 +17154,7 @@
       </c>
       <c r="T17" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 09:45 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -16683,6 +17173,11 @@
         </is>
       </c>
       <c r="X17" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -16786,7 +17281,7 @@
       </c>
       <c r="T18" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: expect(locator).not.toHaveText(expected) failed</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: expect(locator).not.toHaveText(expected) failed</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -16805,6 +17300,11 @@
         </is>
       </c>
       <c r="X18" t="inlineStr">
+        <is>
+          <t>failed: expect(locator).not.toHaveText(expected) failed</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
         <is>
           <t>failed: expect(locator).not.toHaveText(expected) failed</t>
         </is>
@@ -16908,7 +17408,7 @@
       </c>
       <c r="T19" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: expect(locator).not.toContainText(expected) failed</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: expect(locator).not.toContainText(expected) failed</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -16927,6 +17427,11 @@
         </is>
       </c>
       <c r="X19" t="inlineStr">
+        <is>
+          <t>failed: expect(locator).not.toContainText(expected) failed</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
         <is>
           <t>failed: expect(locator).not.toContainText(expected) failed</t>
         </is>
@@ -17030,7 +17535,7 @@
       </c>
       <c r="T20" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 09:45 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -17049,6 +17554,11 @@
         </is>
       </c>
       <c r="X20" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -17152,7 +17662,7 @@
       </c>
       <c r="T21" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 09:45 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -17171,6 +17681,11 @@
         </is>
       </c>
       <c r="X21" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -17274,7 +17789,7 @@
       </c>
       <c r="T22" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 09:45 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -17293,6 +17808,11 @@
         </is>
       </c>
       <c r="X22" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -17396,7 +17916,7 @@
       </c>
       <c r="T23" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 09:45 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -17415,6 +17935,11 @@
         </is>
       </c>
       <c r="X23" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -17518,7 +18043,7 @@
       </c>
       <c r="T24" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 09:45 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -17537,6 +18062,11 @@
         </is>
       </c>
       <c r="X24" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -17640,7 +18170,7 @@
       </c>
       <c r="T25" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: Test timeout of 30000ms exceeded.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Test timeout of 30000ms exceeded.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -17659,6 +18189,11 @@
         </is>
       </c>
       <c r="X25" t="inlineStr">
+        <is>
+          <t>failed: Test timeout of 30000ms exceeded.</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
         <is>
           <t>failed: Test timeout of 30000ms exceeded.</t>
         </is>
@@ -17762,7 +18297,7 @@
       </c>
       <c r="T26" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: Pending until a lower-privilege user is available.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Pending until a lower-privilege user is available.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -17781,6 +18316,11 @@
         </is>
       </c>
       <c r="X26" t="inlineStr">
+        <is>
+          <t>failed: Pending until a lower-privilege user is available.</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
         <is>
           <t>failed: Pending until a lower-privilege user is available.</t>
         </is>
@@ -17884,7 +18424,7 @@
       </c>
       <c r="T27" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: expect(locator).toHaveValue(expected) failed</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: expect(locator).toHaveValue(expected) failed</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -17903,6 +18443,11 @@
         </is>
       </c>
       <c r="X27" t="inlineStr">
+        <is>
+          <t>failed: expect(locator).toHaveValue(expected) failed</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
         <is>
           <t>failed: expect(locator).toHaveValue(expected) failed</t>
         </is>
@@ -17934,6 +18479,11 @@
         </is>
       </c>
       <c r="U30" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
         <is>
           <t>not run</t>
         </is>
@@ -17965,6 +18515,11 @@
           <t>not run</t>
         </is>
       </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -17985,6 +18540,11 @@
           <t>not run</t>
         </is>
       </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -18005,6 +18565,11 @@
           <t>not run</t>
         </is>
       </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -18025,6 +18590,11 @@
           <t>not run</t>
         </is>
       </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -18045,6 +18615,11 @@
           <t>not run</t>
         </is>
       </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -18060,6 +18635,11 @@
           <t>not run</t>
         </is>
       </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -18147,6 +18727,11 @@
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
         </is>
       </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -18234,6 +18819,11 @@
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
         </is>
       </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -18321,6 +18911,11 @@
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
         </is>
       </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -18408,6 +19003,11 @@
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
         </is>
       </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -18495,6 +19095,11 @@
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
         </is>
       </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -18580,6 +19185,11 @@
       <c r="T43" t="inlineStr">
         <is>
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>not run</t>
         </is>
       </c>
     </row>
@@ -18596,7 +19206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X39"/>
+  <dimension ref="A1:Y39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="38.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="16" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -18611,11 +19221,14 @@
     <col width="32.5703125" bestFit="1" customWidth="1" min="13" max="13"/>
     <col width="38.5703125" bestFit="1" customWidth="1" min="14" max="14"/>
     <col hidden="1" width="12" customWidth="1" min="15" max="16"/>
+    <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
     <col hidden="1" width="14" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
     <col width="28" customWidth="1" min="21" max="22"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" thickBot="1">
@@ -18739,6 +19352,11 @@
           <t>Test run @ 09:45 PM @ 02/04/26</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Test run @ 11:11 PM @ 03/04/26</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -18838,7 +19456,7 @@
       </c>
       <c r="T2" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 09:45 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -18857,6 +19475,11 @@
         </is>
       </c>
       <c r="X2" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -18960,7 +19583,7 @@
       </c>
       <c r="T3" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 09:45 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -18979,6 +19602,11 @@
         </is>
       </c>
       <c r="X3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -19082,7 +19710,7 @@
       </c>
       <c r="T4" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: expect(locator).toHaveValue(expected) failed</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: expect(locator).toHaveValue(expected) failed</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -19101,6 +19729,11 @@
         </is>
       </c>
       <c r="X4" t="inlineStr">
+        <is>
+          <t>failed: expect(locator).toHaveValue(expected) failed</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>failed: expect(locator).toHaveValue(expected) failed</t>
         </is>
@@ -19204,7 +19837,7 @@
       </c>
       <c r="T5" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 09:45 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -19223,6 +19856,11 @@
         </is>
       </c>
       <c r="X5" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -19326,7 +19964,7 @@
       </c>
       <c r="T6" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: expect(locator).toHaveValue(expected) failed</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: expect(locator).toHaveValue(expected) failed</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -19345,6 +19983,11 @@
         </is>
       </c>
       <c r="X6" t="inlineStr">
+        <is>
+          <t>failed: expect(locator).toHaveValue(expected) failed</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>failed: expect(locator).toHaveValue(expected) failed</t>
         </is>
@@ -19448,7 +20091,7 @@
       </c>
       <c r="T7" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: expect(locator).toBeVisible() failed</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: expect(locator).toBeVisible() failed</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -19467,6 +20110,11 @@
         </is>
       </c>
       <c r="X7" t="inlineStr">
+        <is>
+          <t>failed: expect(locator).toBeVisible() failed</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>failed: expect(locator).toBeVisible() failed</t>
         </is>
@@ -19570,7 +20218,7 @@
       </c>
       <c r="T8" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: Current local Manage WRCF UI does not expose a stable Apply-button flow to exercise separately.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current local Manage WRCF UI does not expose a stable Apply-button flow to exercise separately.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -19591,6 +20239,11 @@
       <c r="X8" t="inlineStr">
         <is>
           <t>failed: Current local Manage WRCF UI does not expose a stable Apply-button...</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>failed: Current local Manage WRCF UI does not expose a stable Apply-button flow to exercise separa</t>
         </is>
       </c>
     </row>
@@ -19692,7 +20345,7 @@
       </c>
       <c r="T9" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 09:45 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -19711,6 +20364,11 @@
         </is>
       </c>
       <c r="X9" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -19804,17 +20462,17 @@
       </c>
       <c r="R10" s="11" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="S10" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T10" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 09:45 PM 02/04/26 rerun.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: No selectable options were available.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -19835,6 +20493,11 @@
       <c r="X10" t="inlineStr">
         <is>
           <t>passed</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>failed: No selectable options were available.</t>
         </is>
       </c>
     </row>
@@ -19936,7 +20599,7 @@
       </c>
       <c r="T11" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: The current UI does not expose a reliable default-selected FG state on initial page load.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: The current UI does not expose a reliable default-selected FG state on initial page load.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -19957,6 +20620,11 @@
       <c r="X11" t="inlineStr">
         <is>
           <t>failed: The current UI does not expose a reliable default-selected FG state...</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>failed: The current UI does not expose a reliable default-selected FG state on initial page load.</t>
         </is>
       </c>
     </row>
@@ -20058,7 +20726,7 @@
       </c>
       <c r="T12" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 09:45 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -20077,6 +20745,11 @@
         </is>
       </c>
       <c r="X12" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -20180,7 +20853,7 @@
       </c>
       <c r="T13" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: The current UI does not expose a reliable default-selected PWO state on initial page load.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: The current UI does not expose a reliable default-selected PWO state on initial page load.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -20201,6 +20874,11 @@
       <c r="X13" t="inlineStr">
         <is>
           <t>failed: The current UI does not expose a reliable default-selected PWO stat...</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>failed: The current UI does not expose a reliable default-selected PWO state on initial page load.</t>
         </is>
       </c>
     </row>
@@ -20302,7 +20980,7 @@
       </c>
       <c r="T14" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: Needs deterministic seeded hierarchy data and selection-reset assertions across all lower columns.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs deterministic seeded hierarchy data and selection-reset assertions across all lower columns.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -20323,6 +21001,11 @@
       <c r="X14" t="inlineStr">
         <is>
           <t>failed: Needs deterministic seeded hierarchy data and selection-reset asser...</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">failed: Needs deterministic seeded hierarchy data and selection-reset assertions across all lower </t>
         </is>
       </c>
     </row>
@@ -20414,17 +21097,17 @@
       </c>
       <c r="R15" s="11" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="S15" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T15" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 09:45 PM 02/04/26 rerun.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: No selectable options were available.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -20445,6 +21128,11 @@
       <c r="X15" t="inlineStr">
         <is>
           <t>passed</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>failed: No selectable options were available.</t>
         </is>
       </c>
     </row>
@@ -20546,7 +21234,7 @@
       </c>
       <c r="T16" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: The current UI does not expose a reliable default-selected SWO state on initial page load.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: The current UI does not expose a reliable default-selected SWO state on initial page load.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -20567,6 +21255,11 @@
       <c r="X16" t="inlineStr">
         <is>
           <t>failed: The current UI does not expose a reliable default-selected SWO stat...</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>failed: The current UI does not expose a reliable default-selected SWO state on initial page load.</t>
         </is>
       </c>
     </row>
@@ -20668,7 +21361,7 @@
       </c>
       <c r="T17" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: Needs deterministic seeded PWO/SWO hierarchy data to verify lower-column resets.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs deterministic seeded PWO/SWO hierarchy data to verify lower-column resets.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -20689,6 +21382,11 @@
       <c r="X17" t="inlineStr">
         <is>
           <t>failed: Needs deterministic seeded PWO/SWO hierarchy data to verify lower-c...</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>failed: Needs deterministic seeded PWO/SWO hierarchy data to verify lower-column resets.</t>
         </is>
       </c>
     </row>
@@ -20790,7 +21488,7 @@
       </c>
       <c r="T18" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 09:45 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -20809,6 +21507,11 @@
         </is>
       </c>
       <c r="X18" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -20912,7 +21615,7 @@
       </c>
       <c r="T19" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: Requires seeded CI marking data and a stable UI indicator contract for marked capabilities.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Requires seeded CI marking data and a stable UI indicator contract for marked capabilities.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -20933,6 +21636,11 @@
       <c r="X19" t="inlineStr">
         <is>
           <t>failed: Requires seeded CI marking data and a stable UI indicator contract...</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>failed: Requires seeded CI marking data and a stable UI indicator contract for marked capabilities</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21742,7 @@
       </c>
       <c r="T20" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: Requires mixed active/inactive capability fixtures across published history.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Requires mixed active/inactive capability fixtures across published history.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -21055,6 +21763,11 @@
       <c r="X20" t="inlineStr">
         <is>
           <t>failed: Requires mixed active/inactive capability fixtures across published...</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>failed: Requires mixed active/inactive capability fixtures across published history.</t>
         </is>
       </c>
     </row>
@@ -21156,7 +21869,7 @@
       </c>
       <c r="T21" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: No selectable options were available.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: expect(received).toEqual(expected) // deep equality</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -21177,6 +21890,11 @@
       <c r="X21" t="inlineStr">
         <is>
           <t>failed: No selectable options were available.</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>failed: expect(received).toEqual(expected) // deep equality</t>
         </is>
       </c>
     </row>
@@ -21278,7 +21996,7 @@
       </c>
       <c r="T22" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: Requires seeded CI/proficiency marking data and a stable UI marker contract.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Requires seeded CI/proficiency marking data and a stable UI marker contract.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -21299,6 +22017,11 @@
       <c r="X22" t="inlineStr">
         <is>
           <t>failed: Requires seeded CI/proficiency marking data and a stable UI marker...</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>failed: Requires seeded CI/proficiency marking data and a stable UI marker contract.</t>
         </is>
       </c>
     </row>
@@ -21400,7 +22123,7 @@
       </c>
       <c r="T23" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: Needs DB-backed comparison between UI marks and authoritative CI combinations.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs DB-backed comparison between UI marks and authoritative CI combinations.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -21421,6 +22144,11 @@
       <c r="X23" t="inlineStr">
         <is>
           <t>failed: Needs DB-backed comparison between UI marks and authoritative CI co...</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>failed: Needs DB-backed comparison between UI marks and authoritative CI combinations.</t>
         </is>
       </c>
     </row>
@@ -21522,7 +22250,7 @@
       </c>
       <c r="T24" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: Needs duplicate-like seeded data across versions to prove visual inflation does not happen.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs duplicate-like seeded data across versions to prove visual inflation does not happen.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -21543,6 +22271,11 @@
       <c r="X24" t="inlineStr">
         <is>
           <t>failed: Needs duplicate-like seeded data across versions to prove visual in...</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>failed: Needs duplicate-like seeded data across versions to prove visual inflation does not happen</t>
         </is>
       </c>
     </row>
@@ -21644,7 +22377,7 @@
       </c>
       <c r="T25" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: Needs published-vs-draft split data in the local environment.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs published-vs-draft split data in the local environment.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -21663,6 +22396,11 @@
         </is>
       </c>
       <c r="X25" t="inlineStr">
+        <is>
+          <t>failed: Needs published-vs-draft split data in the local environment.</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
         <is>
           <t>failed: Needs published-vs-draft split data in the local environment.</t>
         </is>
@@ -21766,7 +22504,7 @@
       </c>
       <c r="T26" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: Needs mixed active/inactive hierarchy fixtures in the selected industry.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs mixed active/inactive hierarchy fixtures in the selected industry.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -21787,6 +22525,11 @@
       <c r="X26" t="inlineStr">
         <is>
           <t>failed: Needs mixed active/inactive hierarchy fixtures in the selected indu...</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>failed: Needs mixed active/inactive hierarchy fixtures in the selected industry.</t>
         </is>
       </c>
     </row>
@@ -21888,7 +22631,7 @@
       </c>
       <c r="T27" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: Needs a seeded industry that has no active published FG.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a seeded industry that has no active published FG.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -21907,6 +22650,11 @@
         </is>
       </c>
       <c r="X27" t="inlineStr">
+        <is>
+          <t>failed: Needs a seeded industry that has no active published FG.</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
         <is>
           <t>failed: Needs a seeded industry that has no active published FG.</t>
         </is>
@@ -22010,7 +22758,7 @@
       </c>
       <c r="T28" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: Needs a seeded FG that has no PWO children.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a seeded FG that has no PWO children.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -22029,6 +22777,11 @@
         </is>
       </c>
       <c r="X28" t="inlineStr">
+        <is>
+          <t>failed: Needs a seeded FG that has no PWO children.</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
         <is>
           <t>failed: Needs a seeded FG that has no PWO children.</t>
         </is>
@@ -22132,7 +22885,7 @@
       </c>
       <c r="T29" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: Needs a seeded PWO that has no SWO children.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a seeded PWO that has no SWO children.</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -22151,6 +22904,11 @@
         </is>
       </c>
       <c r="X29" t="inlineStr">
+        <is>
+          <t>failed: Needs a seeded PWO that has no SWO children.</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
         <is>
           <t>failed: Needs a seeded PWO that has no SWO children.</t>
         </is>
@@ -22254,7 +23012,7 @@
       </c>
       <c r="T30" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: Needs cross-tenant seeded data and an authoritative comparison source.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs cross-tenant seeded data and an authoritative comparison source.</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -22273,6 +23031,11 @@
         </is>
       </c>
       <c r="X30" t="inlineStr">
+        <is>
+          <t>failed: Needs cross-tenant seeded data and an authoritative comparison source.</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
         <is>
           <t>failed: Needs cross-tenant seeded data and an authoritative comparison source.</t>
         </is>
@@ -22376,7 +23139,7 @@
       </c>
       <c r="T31" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: Needs a lower-privilege user account for authorization checks.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a lower-privilege user account for authorization checks.</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -22395,6 +23158,11 @@
         </is>
       </c>
       <c r="X31" t="inlineStr">
+        <is>
+          <t>failed: Needs a lower-privilege user account for authorization checks.</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
         <is>
           <t>failed: Needs a lower-privilege user account for authorization checks.</t>
         </is>
@@ -22498,7 +23266,7 @@
       </c>
       <c r="T32" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: Needs a stable Apply-based filtering workflow in the current UI.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a stable Apply-based filtering workflow in the current UI.</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -22517,6 +23285,11 @@
         </is>
       </c>
       <c r="X32" t="inlineStr">
+        <is>
+          <t>failed: Needs a stable Apply-based filtering workflow in the current UI.</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
         <is>
           <t>failed: Needs a stable Apply-based filtering workflow in the current UI.</t>
         </is>
@@ -22620,7 +23393,7 @@
       </c>
       <c r="T33" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: Needs seeded partial-CI business-rule data for the selected SWO.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs seeded partial-CI business-rule data for the selected SWO.</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -22639,6 +23412,11 @@
         </is>
       </c>
       <c r="X33" t="inlineStr">
+        <is>
+          <t>failed: Needs seeded partial-CI business-rule data for the selected SWO.</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
         <is>
           <t>failed: Needs seeded partial-CI business-rule data for the selected SWO.</t>
         </is>
@@ -22742,7 +23520,7 @@
       </c>
       <c r="T34" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: Needs CI creation or a DB-backed mark-validation workflow.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs CI creation or a DB-backed mark-validation workflow.</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -22761,6 +23539,11 @@
         </is>
       </c>
       <c r="X34" t="inlineStr">
+        <is>
+          <t>failed: Needs CI creation or a DB-backed mark-validation workflow.</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
         <is>
           <t>failed: Needs CI creation or a DB-backed mark-validation workflow.</t>
         </is>
@@ -22864,7 +23647,7 @@
       </c>
       <c r="T35" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: Needs a high-volume seeded industry dataset and explicit performance thresholds.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a high-volume seeded industry dataset and explicit performance thresholds.</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -22885,6 +23668,11 @@
       <c r="X35" t="inlineStr">
         <is>
           <t>failed: Needs a high-volume seeded industry dataset and explicit performanc...</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>failed: Needs a high-volume seeded industry dataset and explicit performance thresholds.</t>
         </is>
       </c>
     </row>
@@ -22986,7 +23774,7 @@
       </c>
       <c r="T36" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 09:45 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -23005,6 +23793,11 @@
         </is>
       </c>
       <c r="X36" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -23108,7 +23901,7 @@
       </c>
       <c r="T37" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 09:45 PM 02/04/26 rerun: Needs multiple capability mark states with seeded CI data to validate stale-mark cleanup.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs multiple capability mark states with seeded CI data to validate stale-mark cleanup.</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -23129,6 +23922,11 @@
       <c r="X37" t="inlineStr">
         <is>
           <t>failed: Needs multiple capability mark states with seeded CI data to valida...</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>failed: Needs multiple capability mark states with seeded CI data to validate stale-mark cleanup.</t>
         </is>
       </c>
     </row>
@@ -23221,6 +24019,11 @@
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
         </is>
       </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -23309,6 +24112,11 @@
       <c r="T39" s="13" t="inlineStr">
         <is>
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>not run</t>
         </is>
       </c>
     </row>
@@ -23325,7 +24133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y29"/>
+  <dimension ref="A1:Z29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="28.28515625" defaultRowHeight="15"/>
   <cols>
     <col width="11.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -23345,6 +24153,8 @@
     <col width="22" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
     <col width="28" customWidth="1" min="21" max="22"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -23473,6 +24283,11 @@
           <t>Test run @ 08:17 PM @ 02/04/26</t>
         </is>
       </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Test run @ 11:11 PM @ 03/04/26</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
@@ -23562,17 +24377,17 @@
       </c>
       <c r="R2" s="11" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="S2" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T2" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Steel Manufacturing"</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -23598,6 +24413,11 @@
       <c r="Y2" t="inlineStr">
         <is>
           <t>passed</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>failed: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Ste</t>
         </is>
       </c>
     </row>
@@ -23689,17 +24509,17 @@
       </c>
       <c r="R3" s="11" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="S3" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T3" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Steel Manufacturing"</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -23725,6 +24545,11 @@
       <c r="Y3" t="inlineStr">
         <is>
           <t>passed</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>failed: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Ste</t>
         </is>
       </c>
     </row>
@@ -23816,17 +24641,17 @@
       </c>
       <c r="R4" s="11" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="S4" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T4" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Steel Manufacturing"</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -23852,6 +24677,11 @@
       <c r="Y4" t="inlineStr">
         <is>
           <t>passed</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>failed: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Ste</t>
         </is>
       </c>
     </row>
@@ -23943,17 +24773,17 @@
       </c>
       <c r="R5" s="11" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="S5" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T5" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Steel Manufacturing"</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -23979,6 +24809,11 @@
       <c r="Y5" t="inlineStr">
         <is>
           <t>passed</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>failed: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Ste</t>
         </is>
       </c>
     </row>
@@ -24070,17 +24905,17 @@
       </c>
       <c r="R6" s="11" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="S6" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T6" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Steel Manufacturing"</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -24106,6 +24941,11 @@
       <c r="Y6" t="inlineStr">
         <is>
           <t>passed</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>failed: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Ste</t>
         </is>
       </c>
     </row>
@@ -24197,17 +25037,17 @@
       </c>
       <c r="R7" s="11" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="S7" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T7" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Steel Manufacturing"</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -24233,6 +25073,11 @@
       <c r="Y7" t="inlineStr">
         <is>
           <t>passed</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>failed: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Ste</t>
         </is>
       </c>
     </row>
@@ -24324,17 +25169,17 @@
       </c>
       <c r="R8" s="11" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="S8" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T8" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Steel Manufacturing"</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -24360,6 +25205,11 @@
       <c r="Y8" t="inlineStr">
         <is>
           <t>passed</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>failed: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Ste</t>
         </is>
       </c>
     </row>
@@ -24451,17 +25301,17 @@
       </c>
       <c r="R9" s="11" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="S9" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T9" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Steel Manufacturing"</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -24487,6 +25337,11 @@
       <c r="Y9" t="inlineStr">
         <is>
           <t>passed</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>failed: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Ste</t>
         </is>
       </c>
     </row>
@@ -24588,7 +25443,7 @@
       </c>
       <c r="T10" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: expect(locator).toContainText(expected) failed</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Steel Manufacturing"</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -24614,6 +25469,11 @@
       <c r="Y10" t="inlineStr">
         <is>
           <t>failed: expect(locator).toContainText(expected) failed</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>failed: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Ste</t>
         </is>
       </c>
     </row>
@@ -24715,7 +25575,7 @@
       </c>
       <c r="T11" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: expect(locator).toContainText(expected) failed</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Steel Manufacturing"</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -24741,6 +25601,11 @@
       <c r="Y11" t="inlineStr">
         <is>
           <t>failed: expect(locator).toContainText(expected) failed</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>failed: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Ste</t>
         </is>
       </c>
     </row>
@@ -24832,17 +25697,17 @@
       </c>
       <c r="R12" s="11" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="S12" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T12" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Steel Manufacturing"</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -24868,6 +25733,11 @@
       <c r="Y12" t="inlineStr">
         <is>
           <t>passed</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>failed: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Ste</t>
         </is>
       </c>
     </row>
@@ -24959,17 +25829,17 @@
       </c>
       <c r="R13" s="11" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="S13" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T13" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Steel Manufacturing"</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -24995,6 +25865,11 @@
       <c r="Y13" t="inlineStr">
         <is>
           <t>passed</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>failed: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Ste</t>
         </is>
       </c>
     </row>
@@ -25086,17 +25961,17 @@
       </c>
       <c r="R14" s="11" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="S14" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T14" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Steel Manufacturing"</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -25122,6 +25997,11 @@
       <c r="Y14" t="inlineStr">
         <is>
           <t>passed</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>failed: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Ste</t>
         </is>
       </c>
     </row>
@@ -25223,7 +26103,7 @@
       </c>
       <c r="T15" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: expect(received).toEqual(expected) // deep equality</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Steel Manufacturing"</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -25249,6 +26129,11 @@
       <c r="Y15" t="inlineStr">
         <is>
           <t>failed: expect(received).toEqual(expected) // deep equality</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>failed: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Ste</t>
         </is>
       </c>
     </row>
@@ -25340,17 +26225,17 @@
       </c>
       <c r="R16" s="11" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="S16" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T16" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Steel Manufacturing"</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -25376,6 +26261,11 @@
       <c r="Y16" t="inlineStr">
         <is>
           <t>passed</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>failed: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Ste</t>
         </is>
       </c>
     </row>
@@ -25467,17 +26357,17 @@
       </c>
       <c r="R17" s="11" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="S17" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T17" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Steel Manufacturing"</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -25503,6 +26393,11 @@
       <c r="Y17" t="inlineStr">
         <is>
           <t>passed</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>failed: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Ste</t>
         </is>
       </c>
     </row>
@@ -25594,17 +26489,17 @@
       </c>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="S18" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T18" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Steel Manufacturing"</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -25630,6 +26525,11 @@
       <c r="Y18" t="inlineStr">
         <is>
           <t>passed</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>failed: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Ste</t>
         </is>
       </c>
     </row>
@@ -25721,17 +26621,17 @@
       </c>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="S19" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T19" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Steel Manufacturing"</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -25757,6 +26657,11 @@
       <c r="Y19" t="inlineStr">
         <is>
           <t>passed</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>failed: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Ste</t>
         </is>
       </c>
     </row>
@@ -25858,7 +26763,7 @@
       </c>
       <c r="T20" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: expect(locator).toContainText(expected) failed</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Steel Manufacturing"</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -25884,6 +26789,11 @@
       <c r="Y20" t="inlineStr">
         <is>
           <t>failed: expect(locator).toContainText(expected) failed</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>failed: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Ste</t>
         </is>
       </c>
     </row>
@@ -25975,17 +26885,17 @@
       </c>
       <c r="R21" s="11" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="S21" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T21" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Steel Manufacturing"</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -26011,6 +26921,11 @@
       <c r="Y21" t="inlineStr">
         <is>
           <t>passed</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>failed: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Ste</t>
         </is>
       </c>
     </row>
@@ -26102,17 +27017,17 @@
       </c>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="S22" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T22" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Steel Manufacturing"</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -26138,6 +27053,11 @@
       <c r="Y22" t="inlineStr">
         <is>
           <t>passed</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>failed: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Ste</t>
         </is>
       </c>
     </row>
@@ -26229,17 +27149,17 @@
       </c>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="S23" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T23" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Steel Manufacturing"</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -26265,6 +27185,11 @@
       <c r="Y23" t="inlineStr">
         <is>
           <t>passed</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>failed: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Ste</t>
         </is>
       </c>
     </row>
@@ -26356,17 +27281,17 @@
       </c>
       <c r="R24" s="11" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="S24" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T24" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Steel Manufacturing"</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -26392,6 +27317,11 @@
       <c r="Y24" t="inlineStr">
         <is>
           <t>passed</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>failed: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Ste</t>
         </is>
       </c>
     </row>
@@ -26483,17 +27413,17 @@
       </c>
       <c r="R25" s="11" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="S25" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T25" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Steel Manufacturing"</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -26519,6 +27449,11 @@
       <c r="Y25" t="inlineStr">
         <is>
           <t>passed</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>failed: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Ste</t>
         </is>
       </c>
     </row>
@@ -26620,7 +27555,7 @@
       </c>
       <c r="T26" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: expect(locator).toBeVisible() failed</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Steel Manufacturing"</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -26646,6 +27581,11 @@
       <c r="Y26" t="inlineStr">
         <is>
           <t>failed: expect(locator).toBeVisible() failed</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>failed: Waiting for Functional Group rows after selecting sector "Manufacturing" and industry "Ste</t>
         </is>
       </c>
     </row>
@@ -26738,6 +27678,11 @@
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -26828,6 +27773,11 @@
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -26916,6 +27866,11 @@
       <c r="T29" s="13" t="inlineStr">
         <is>
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>not run</t>
         </is>
       </c>
     </row>
@@ -26932,7 +27887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="32.42578125" defaultRowHeight="15"/>
   <cols>
     <col width="12.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -26956,6 +27911,8 @@
     <col width="22" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
     <col width="28" customWidth="1" min="21" max="22"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -27079,6 +28036,11 @@
           <t>Test run @ 08:17 PM @ 02/04/26</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Test run @ 11:11 PM @ 03/04/26</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="45" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
@@ -27178,7 +28140,7 @@
       </c>
       <c r="T2" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -27197,6 +28159,11 @@
         </is>
       </c>
       <c r="X2" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -27300,7 +28267,7 @@
       </c>
       <c r="T3" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -27319,6 +28286,11 @@
         </is>
       </c>
       <c r="X3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -27422,7 +28394,7 @@
       </c>
       <c r="T4" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -27441,6 +28413,11 @@
         </is>
       </c>
       <c r="X4" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -27544,7 +28521,7 @@
       </c>
       <c r="T5" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -27563,6 +28540,11 @@
         </is>
       </c>
       <c r="X5" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -27666,7 +28648,7 @@
       </c>
       <c r="T6" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -27685,6 +28667,11 @@
         </is>
       </c>
       <c r="X6" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -27788,7 +28775,7 @@
       </c>
       <c r="T7" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -27807,6 +28794,11 @@
         </is>
       </c>
       <c r="X7" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -27910,7 +28902,7 @@
       </c>
       <c r="T8" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -27929,6 +28921,11 @@
         </is>
       </c>
       <c r="X8" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -28032,7 +29029,7 @@
       </c>
       <c r="T9" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs a deterministic second FG context and confirmed parent-scoped uniqueness rule.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a deterministic second FG context and confirmed parent-scoped uniqueness rule.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -28053,6 +29050,11 @@
       <c r="X9" t="inlineStr">
         <is>
           <t>failed: second FG context and confirmed parent-scoped uniqueness rule</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>failed: Needs a deterministic second FG context and confirmed parent-scoped uniqueness rule.</t>
         </is>
       </c>
     </row>
@@ -28154,7 +29156,7 @@
       </c>
       <c r="T10" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -28173,6 +29175,11 @@
         </is>
       </c>
       <c r="X10" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -28276,7 +29283,7 @@
       </c>
       <c r="T11" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Current branch data renders the PWO list in a non-alphabetical order; treat as a documented product/data gap until ordering is guaranteed.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current branch data renders the PWO list in a non-alphabetical order; treat as a documented product/data gap until ordering is guaranteed.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -28297,6 +29304,11 @@
       <c r="X11" t="inlineStr">
         <is>
           <t>failed: branch data renders the PWO list in a non-alphabetical order; treat...</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>failed: Current branch data renders the PWO list in a non-alphabetical order; treat as a documente</t>
         </is>
       </c>
     </row>
@@ -28398,7 +29410,7 @@
       </c>
       <c r="T12" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -28417,6 +29429,11 @@
         </is>
       </c>
       <c r="X12" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -28520,7 +29537,7 @@
       </c>
       <c r="T13" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -28539,6 +29556,11 @@
         </is>
       </c>
       <c r="X13" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -28642,7 +29664,7 @@
       </c>
       <c r="T14" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -28661,6 +29683,11 @@
         </is>
       </c>
       <c r="X14" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -28764,7 +29791,7 @@
       </c>
       <c r="T15" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -28783,6 +29810,11 @@
         </is>
       </c>
       <c r="X15" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -28886,7 +29918,7 @@
       </c>
       <c r="T16" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Current local PWO delete behavior has not yet been confirmed with a stable confirmation dialog.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current local PWO delete behavior has not yet been confirmed with a stable confirmation dialog.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -28907,6 +29939,11 @@
       <c r="X16" t="inlineStr">
         <is>
           <t>failed: local PWO delete behavior has not yet been confirmed with a stable...</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>failed: Current local PWO delete behavior has not yet been confirmed with a stable confirmation di</t>
         </is>
       </c>
     </row>
@@ -29008,7 +30045,7 @@
       </c>
       <c r="T17" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -29027,6 +30064,11 @@
         </is>
       </c>
       <c r="X17" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -29130,7 +30172,7 @@
       </c>
       <c r="T18" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs a seeded or newly created SWO child under the target PWO and confirmed delete-block UI behavior.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a seeded or newly created SWO child under the target PWO and confirmed delete-block UI behavior.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -29151,6 +30193,11 @@
       <c r="X18" t="inlineStr">
         <is>
           <t>failed: a seeded or newly created SWO child under the target PWO and confir...</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">failed: Needs a seeded or newly created SWO child under the target PWO and confirmed delete-block </t>
         </is>
       </c>
     </row>
@@ -29252,7 +30299,7 @@
       </c>
       <c r="T19" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -29271,6 +30318,11 @@
         </is>
       </c>
       <c r="X19" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -29374,7 +30426,7 @@
       </c>
       <c r="T20" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -29393,6 +30445,11 @@
         </is>
       </c>
       <c r="X20" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -29496,7 +30553,7 @@
       </c>
       <c r="T21" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs confirmed Dependency Links field presence in the current local PWO popup.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs confirmed Dependency Links field presence in the current local PWO popup.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -29517,6 +30574,11 @@
       <c r="X21" t="inlineStr">
         <is>
           <t>failed: confirmed Dependency Links field presence in the current local PWO...</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>failed: Needs confirmed Dependency Links field presence in the current local PWO popup.</t>
         </is>
       </c>
     </row>
@@ -29609,6 +30671,11 @@
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
         </is>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -29699,6 +30766,11 @@
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
         </is>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -29789,6 +30861,11 @@
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
         </is>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -29877,6 +30954,11 @@
       <c r="T25" s="13" t="inlineStr">
         <is>
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>not run</t>
         </is>
       </c>
     </row>
@@ -29892,7 +30974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="31" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -29913,6 +30995,8 @@
     <col width="22" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
     <col width="28" customWidth="1" min="21" max="22"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -30036,6 +31120,11 @@
           <t>Test run @ 08:17 PM @ 02/04/26</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Test run @ 11:11 PM @ 03/04/26</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="45" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
@@ -30135,7 +31224,7 @@
       </c>
       <c r="T2" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -30154,6 +31243,11 @@
         </is>
       </c>
       <c r="X2" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -30257,7 +31351,7 @@
       </c>
       <c r="T3" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -30276,6 +31370,11 @@
         </is>
       </c>
       <c r="X3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -30379,7 +31478,7 @@
       </c>
       <c r="T4" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -30398,6 +31497,11 @@
         </is>
       </c>
       <c r="X4" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -30501,7 +31605,7 @@
       </c>
       <c r="T5" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -30520,6 +31624,11 @@
         </is>
       </c>
       <c r="X5" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -30623,7 +31732,7 @@
       </c>
       <c r="T6" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -30642,6 +31751,11 @@
         </is>
       </c>
       <c r="X6" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -30745,7 +31859,7 @@
       </c>
       <c r="T7" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -30764,6 +31878,11 @@
         </is>
       </c>
       <c r="X7" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -30867,7 +31986,7 @@
       </c>
       <c r="T8" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -30886,6 +32005,11 @@
         </is>
       </c>
       <c r="X8" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -30989,7 +32113,7 @@
       </c>
       <c r="T9" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs a deterministic second PWO context and confirmed parent-scoped uniqueness rule.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a deterministic second PWO context and confirmed parent-scoped uniqueness rule.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -31010,6 +32134,11 @@
       <c r="X9" t="inlineStr">
         <is>
           <t>failed: second PWO context and confirmed parent-scoped uniqueness rule</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>failed: Needs a deterministic second PWO context and confirmed parent-scoped uniqueness rule.</t>
         </is>
       </c>
     </row>
@@ -31111,7 +32240,7 @@
       </c>
       <c r="T10" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -31130,6 +32259,11 @@
         </is>
       </c>
       <c r="X10" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -31233,7 +32367,7 @@
       </c>
       <c r="T11" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: expect(received).toEqual(expected) // deep equality</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: expect(received).toEqual(expected) // deep equality</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -31252,6 +32386,11 @@
         </is>
       </c>
       <c r="X11" t="inlineStr">
+        <is>
+          <t>failed: expect(received).toEqual(expected) // deep equality</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>failed: expect(received).toEqual(expected) // deep equality</t>
         </is>
@@ -31355,7 +32494,7 @@
       </c>
       <c r="T12" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -31374,6 +32513,11 @@
         </is>
       </c>
       <c r="X12" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -31477,7 +32621,7 @@
       </c>
       <c r="T13" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -31496,6 +32640,11 @@
         </is>
       </c>
       <c r="X13" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -31599,7 +32748,7 @@
       </c>
       <c r="T14" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -31618,6 +32767,11 @@
         </is>
       </c>
       <c r="X14" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -31721,7 +32875,7 @@
       </c>
       <c r="T15" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -31740,6 +32894,11 @@
         </is>
       </c>
       <c r="X15" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -31843,7 +33002,7 @@
       </c>
       <c r="T16" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Current local SWO delete behavior has not yet been confirmed with a stable confirmation dialog.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current local SWO delete behavior has not yet been confirmed with a stable confirmation dialog.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -31864,6 +33023,11 @@
       <c r="X16" t="inlineStr">
         <is>
           <t>failed: local SWO delete behavior has not yet been confirmed with a stable...</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>failed: Current local SWO delete behavior has not yet been confirmed with a stable confirmation di</t>
         </is>
       </c>
     </row>
@@ -31965,7 +33129,7 @@
       </c>
       <c r="T17" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -31984,6 +33148,11 @@
         </is>
       </c>
       <c r="X17" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -32087,7 +33256,7 @@
       </c>
       <c r="T18" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs seeded downstream mapping data and confirmed delete-block UI behavior.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs seeded downstream mapping data and confirmed delete-block UI behavior.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -32108,6 +33277,11 @@
       <c r="X18" t="inlineStr">
         <is>
           <t>failed: seeded downstream mapping data and confirmed delete-block UI behavior</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>failed: Needs seeded downstream mapping data and confirmed delete-block UI behavior.</t>
         </is>
       </c>
     </row>
@@ -32209,7 +33383,7 @@
       </c>
       <c r="T19" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -32228,6 +33402,11 @@
         </is>
       </c>
       <c r="X19" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -32331,7 +33510,7 @@
       </c>
       <c r="T20" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -32350,6 +33529,11 @@
         </is>
       </c>
       <c r="X20" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -32453,7 +33637,7 @@
       </c>
       <c r="T21" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs CI Mapping workflow coverage and stable downstream selection assertions.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs CI Mapping workflow coverage and stable downstream selection assertions.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -32474,6 +33658,11 @@
       <c r="X21" t="inlineStr">
         <is>
           <t>failed: CI Mapping workflow coverage and stable downstream selection assert...</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>failed: Needs CI Mapping workflow coverage and stable downstream selection assertions.</t>
         </is>
       </c>
     </row>
@@ -32566,6 +33755,11 @@
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
         </is>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -32656,6 +33850,11 @@
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
         </is>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -32746,6 +33945,11 @@
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
         </is>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -32834,6 +34038,11 @@
       <c r="T25" s="13" t="inlineStr">
         <is>
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>not run</t>
         </is>
       </c>
     </row>
@@ -32849,7 +34058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y38"/>
+  <dimension ref="A1:Z38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="35.140625" defaultRowHeight="15"/>
   <cols>
     <col width="14.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -32869,6 +34078,8 @@
     <col width="22" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
     <col width="28" customWidth="1" min="21" max="22"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -32997,6 +34208,11 @@
           <t>Test run @ 08:17 PM @ 02/04/26</t>
         </is>
       </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Test run @ 11:11 PM @ 03/04/26</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="75" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
@@ -33096,7 +34312,7 @@
       </c>
       <c r="T2" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -33120,6 +34336,11 @@
         </is>
       </c>
       <c r="Y2" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -33223,7 +34444,7 @@
       </c>
       <c r="T3" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -33247,6 +34468,11 @@
         </is>
       </c>
       <c r="Y3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -33350,7 +34576,7 @@
       </c>
       <c r="T4" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -33374,6 +34600,11 @@
         </is>
       </c>
       <c r="Y4" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -33477,7 +34708,7 @@
       </c>
       <c r="T5" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -33501,6 +34732,11 @@
         </is>
       </c>
       <c r="Y5" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -33594,17 +34830,17 @@
       </c>
       <c r="R6" s="11" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="S6" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T6" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: expect(locator).toHaveText(expected) failed</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -33630,6 +34866,11 @@
       <c r="Y6" t="inlineStr">
         <is>
           <t>passed</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>failed: expect(locator).toHaveText(expected) failed</t>
         </is>
       </c>
     </row>
@@ -33731,7 +34972,7 @@
       </c>
       <c r="T7" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -33755,6 +34996,11 @@
         </is>
       </c>
       <c r="Y7" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -33858,7 +35104,7 @@
       </c>
       <c r="T8" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs at least two deterministic hierarchy paths with different saved CI states.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs at least two deterministic hierarchy paths with different saved CI states.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -33884,6 +35130,11 @@
       <c r="Y8" t="inlineStr">
         <is>
           <t>failed: at least two deterministic hierarchy paths with different saved CI...</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>failed: Needs at least two deterministic hierarchy paths with different saved CI states.</t>
         </is>
       </c>
     </row>
@@ -33985,7 +35236,7 @@
       </c>
       <c r="T9" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs a deterministic SWO with different saved states across multiple capabilities.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a deterministic SWO with different saved states across multiple capabilities.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -34011,6 +35262,11 @@
       <c r="Y9" t="inlineStr">
         <is>
           <t>failed: SWO with different saved states across multiple capabilities</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>failed: Needs a deterministic SWO with different saved states across multiple capabilities.</t>
         </is>
       </c>
     </row>
@@ -34107,12 +35363,12 @@
       </c>
       <c r="S10" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T10" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs live save execution plus deterministic cleanup for created CI records.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs live save execution plus deterministic cleanup for created CI records.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -34138,6 +35394,11 @@
       <c r="Y10" t="inlineStr">
         <is>
           <t>failed: live save execution plus deterministic cleanup for created CI records</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>failed: Needs live save execution plus deterministic cleanup for created CI records.</t>
         </is>
       </c>
     </row>
@@ -34239,7 +35500,7 @@
       </c>
       <c r="T11" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Current UI keeps parent pending cache outside the popup; workbook expects discard-on-close behavior.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current UI keeps parent pending cache outside the popup; workbook expects discard-on-close behavior.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -34265,6 +35526,11 @@
       <c r="Y11" t="inlineStr">
         <is>
           <t>failed: UI keeps parent pending cache outside the popup; workbook expects d...</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>failed: Current UI keeps parent pending cache outside the popup; workbook expects discard-on-close</t>
         </is>
       </c>
     </row>
@@ -34366,7 +35632,7 @@
       </c>
       <c r="T12" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -34390,6 +35656,11 @@
         </is>
       </c>
       <c r="Y12" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -34493,7 +35764,7 @@
       </c>
       <c r="T13" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -34517,6 +35788,11 @@
         </is>
       </c>
       <c r="Y13" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -34610,17 +35886,17 @@
       </c>
       <c r="R14" s="11" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="S14" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T14" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: expect(received).resolves.toEqual(expected) // deep equality</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -34646,6 +35922,11 @@
       <c r="Y14" t="inlineStr">
         <is>
           <t>passed</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>failed: expect(received).resolves.toEqual(expected) // deep equality</t>
         </is>
       </c>
     </row>
@@ -34747,7 +36028,7 @@
       </c>
       <c r="T15" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -34771,6 +36052,11 @@
         </is>
       </c>
       <c r="Y15" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -34874,7 +36160,7 @@
       </c>
       <c r="T16" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -34898,6 +36184,11 @@
         </is>
       </c>
       <c r="Y16" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -35001,7 +36292,7 @@
       </c>
       <c r="T17" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Current popup groups preserve API/cache order; workbook expects explicit alphabetical ordering.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current popup groups preserve API/cache order; workbook expects explicit alphabetical ordering.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -35027,6 +36318,11 @@
       <c r="Y17" t="inlineStr">
         <is>
           <t>failed: popup groups preserve API/cache order; workbook expects explicit al...</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>failed: Current popup groups preserve API/cache order; workbook expects explicit alphabetical orde</t>
         </is>
       </c>
     </row>
@@ -35128,7 +36424,7 @@
       </c>
       <c r="T18" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -35152,6 +36448,11 @@
         </is>
       </c>
       <c r="Y18" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -35255,7 +36556,7 @@
       </c>
       <c r="T19" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -35279,6 +36580,11 @@
         </is>
       </c>
       <c r="Y19" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -35382,7 +36688,7 @@
       </c>
       <c r="T20" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -35406,6 +36712,11 @@
         </is>
       </c>
       <c r="Y20" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -35509,7 +36820,7 @@
       </c>
       <c r="T21" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: expect(received).toBeGreaterThan(expected)</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: expect(received).toBeGreaterThan(expected)</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -35533,6 +36844,11 @@
         </is>
       </c>
       <c r="Y21" t="inlineStr">
+        <is>
+          <t>failed: expect(received).toBeGreaterThan(expected)</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
         <is>
           <t>failed: expect(received).toBeGreaterThan(expected)</t>
         </is>
@@ -35636,7 +36952,7 @@
       </c>
       <c r="T22" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs at least one pending CI row in the popup before delete/remove can be verified.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs at least one pending CI row in the popup before delete/remove can be verified.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -35662,6 +36978,11 @@
       <c r="Y22" t="inlineStr">
         <is>
           <t>failed: at least one pending CI row in the popup before delete/remove can b...</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>failed: Needs at least one pending CI row in the popup before delete/remove can be verified.</t>
         </is>
       </c>
     </row>
@@ -35763,7 +37084,7 @@
       </c>
       <c r="T23" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs at least one existing saved CI row in the popup.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs at least one existing saved CI row in the popup.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -35789,6 +37110,11 @@
       <c r="Y23" t="inlineStr">
         <is>
           <t>failed: at least one existing saved CI row in the popup</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>failed: Needs at least one existing saved CI row in the popup.</t>
         </is>
       </c>
     </row>
@@ -35890,7 +37216,7 @@
       </c>
       <c r="T24" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs seeded CI rows with downstream skill dependencies.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs seeded CI rows with downstream skill dependencies.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -35916,6 +37242,11 @@
       <c r="Y24" t="inlineStr">
         <is>
           <t>failed: seeded CI rows with downstream skill dependencies</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>failed: Needs seeded CI rows with downstream skill dependencies.</t>
         </is>
       </c>
     </row>
@@ -36012,12 +37343,12 @@
       </c>
       <c r="S25" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T25" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs deterministic childless CI data and cleanup-safe delete coverage.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs deterministic childless CI data and cleanup-safe delete coverage.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -36043,6 +37374,11 @@
       <c r="Y25" t="inlineStr">
         <is>
           <t>failed: childless CI data and cleanup-safe delete coverage</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>failed: Needs deterministic childless CI data and cleanup-safe delete coverage.</t>
         </is>
       </c>
     </row>
@@ -36144,7 +37480,7 @@
       </c>
       <c r="T26" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -36168,6 +37504,11 @@
         </is>
       </c>
       <c r="Y26" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -36271,7 +37612,7 @@
       </c>
       <c r="T27" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Current popup backdrop click closes the dialog; workbook expects a non-dismissable outside-click behavior.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current popup backdrop click closes the dialog; workbook expects a non-dismissable outside-click behavior.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -36297,6 +37638,11 @@
       <c r="Y27" t="inlineStr">
         <is>
           <t>failed: popup backdrop click closes the dialog; workbook expects a non-dism...</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>failed: Current popup backdrop click closes the dialog; workbook expects a non-dismissable outside</t>
         </is>
       </c>
     </row>
@@ -36398,7 +37744,7 @@
       </c>
       <c r="T28" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Current UI retains parent pending cache after dialog close or cancel.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current UI retains parent pending cache after dialog close or cancel.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -36424,6 +37770,11 @@
       <c r="Y28" t="inlineStr">
         <is>
           <t>failed: UI retains parent pending cache after dialog close or cancel</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>failed: Current UI retains parent pending cache after dialog close or cancel.</t>
         </is>
       </c>
     </row>
@@ -36520,12 +37871,12 @@
       </c>
       <c r="S29" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T29" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs live save execution plus deterministic cleanup for created CI records.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs live save execution plus deterministic cleanup for created CI records.</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -36551,6 +37902,11 @@
       <c r="Y29" t="inlineStr">
         <is>
           <t>failed: live save execution plus deterministic cleanup for created CI records</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>failed: Needs live save execution plus deterministic cleanup for created CI records.</t>
         </is>
       </c>
     </row>
@@ -36647,12 +38003,12 @@
       </c>
       <c r="S30" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T30" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs save coverage and deterministic cleanup for created CI records.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs save coverage and deterministic cleanup for created CI records.</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -36678,6 +38034,11 @@
       <c r="Y30" t="inlineStr">
         <is>
           <t>failed: save coverage and deterministic cleanup for created CI records</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>failed: Needs save coverage and deterministic cleanup for created CI records.</t>
         </is>
       </c>
     </row>
@@ -36779,7 +38140,7 @@
       </c>
       <c r="T31" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs controlled duplicate-save setup and backend-visible validation path.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs controlled duplicate-save setup and backend-visible validation path.</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -36805,6 +38166,11 @@
       <c r="Y31" t="inlineStr">
         <is>
           <t>failed: controlled duplicate-save setup and backend-visible validation path</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>failed: Needs controlled duplicate-save setup and backend-visible validation path.</t>
         </is>
       </c>
     </row>
@@ -36906,7 +38272,7 @@
       </c>
       <c r="T32" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Current popup loads sector, industry, and FG options from master lists rather than mapped-only subsets.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current popup loads sector, industry, and FG options from master lists rather than mapped-only subsets.</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -36932,6 +38298,11 @@
       <c r="Y32" t="inlineStr">
         <is>
           <t>failed: popup loads sector, industry, and FG options from master lists rath...</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>failed: Current popup loads sector, industry, and FG options from master lists rather than mapped-</t>
         </is>
       </c>
     </row>
@@ -37028,12 +38399,12 @@
       </c>
       <c r="S33" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T33" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs deterministic multi-FG mapped data in the local environment.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs deterministic multi-FG mapped data in the local environment.</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -37059,6 +38430,11 @@
       <c r="Y33" t="inlineStr">
         <is>
           <t>failed: multi-FG mapped data in the local environment</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>failed: Needs deterministic multi-FG mapped data in the local environment.</t>
         </is>
       </c>
     </row>
@@ -37160,7 +38536,7 @@
       </c>
       <c r="T34" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Current popup groups all parent cache entries regardless of selected FG filter.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current popup groups all parent cache entries regardless of selected FG filter.</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -37186,6 +38562,11 @@
       <c r="Y34" t="inlineStr">
         <is>
           <t>failed: popup groups all parent cache entries regardless of selected FG filter</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>failed: Current popup groups all parent cache entries regardless of selected FG filter.</t>
         </is>
       </c>
     </row>
@@ -37282,12 +38663,12 @@
       </c>
       <c r="S35" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T35" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs backend validation conflicts or mixed save success fixtures.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs backend validation conflicts or mixed save success fixtures.</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -37313,6 +38694,11 @@
       <c r="Y35" t="inlineStr">
         <is>
           <t>failed: backend validation conflicts or mixed save success fixtures</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>failed: Needs backend validation conflicts or mixed save success fixtures.</t>
         </is>
       </c>
     </row>
@@ -37409,12 +38795,12 @@
       </c>
       <c r="S36" s="11" t="inlineStr">
         <is>
-          <t>not-run</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T36" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs live save execution plus deterministic cleanup for created CI records.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs live save execution plus deterministic cleanup for created CI records.</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -37440,6 +38826,11 @@
       <c r="Y36" t="inlineStr">
         <is>
           <t>failed: live save execution plus deterministic cleanup for created CI records</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>failed: Needs live save execution plus deterministic cleanup for created CI records.</t>
         </is>
       </c>
     </row>
@@ -37532,6 +38923,11 @@
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -37620,6 +39016,11 @@
       <c r="T38" s="13" t="inlineStr">
         <is>
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>not run</t>
         </is>
       </c>
     </row>
@@ -37636,7 +39037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X13"/>
+  <dimension ref="A1:Y13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="29.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="14.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -37660,6 +39061,8 @@
     <col width="22" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
     <col width="28" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -37783,6 +39186,11 @@
           <t>Test run @ 08:17 PM @ 02/04/26</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Test run @ 11:11 PM @ 03/04/26</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="75" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
@@ -37882,7 +39290,7 @@
       </c>
       <c r="T2" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Current Industry WRCF + Add Skills navigation only passes industryId, not the full CI filter path.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current Industry WRCF + Add Skills navigation only passes industryId, not the full CI filter path.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -37903,6 +39311,11 @@
       <c r="X2" t="inlineStr">
         <is>
           <t>failed: Industry WRCF + Add Skills navigation only passes industryId, not t...</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>failed: Current Industry WRCF + Add Skills navigation only passes industryId, not the full CI filt</t>
         </is>
       </c>
     </row>
@@ -38004,7 +39417,7 @@
       </c>
       <c r="T3" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Current page loads FG options but leaves the 5 CI filters unselected until the user chooses them.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current page loads FG options but leaves the 5 CI filters unselected until the user chooses them.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -38025,6 +39438,11 @@
       <c r="X3" t="inlineStr">
         <is>
           <t>failed: page loads FG options but leaves the 5 CI filters unselected until...</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>failed: Current page loads FG options but leaves the 5 CI filters unselected until the user choose</t>
         </is>
       </c>
     </row>
@@ -38116,17 +39534,17 @@
       </c>
       <c r="R4" s="11" t="inlineStr">
         <is>
-          <t>fail</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="S4" s="11" t="inlineStr">
         <is>
-          <t>runtime/data</t>
+          <t>none</t>
         </is>
       </c>
       <c r="T4" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Waiting for sector options on Manage Industry WRCF</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -38147,6 +39565,11 @@
       <c r="X4" t="inlineStr">
         <is>
           <t>failed: Waiting for sector options on Manage Industry WRCF</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>passed</t>
         </is>
       </c>
     </row>
@@ -38248,7 +39671,7 @@
       </c>
       <c r="T5" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: expect(received).toEqual(expected) // deep equality</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: expect(received).toEqual(expected) // deep equality</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -38267,6 +39690,11 @@
         </is>
       </c>
       <c r="X5" t="inlineStr">
+        <is>
+          <t>failed: expect(received).toEqual(expected) // deep equality</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>failed: expect(received).toEqual(expected) // deep equality</t>
         </is>
@@ -38370,7 +39798,7 @@
       </c>
       <c r="T6" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Current page requires explicit 5-filter selection unless a ciId query param is provided.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current page requires explicit 5-filter selection unless a ciId query param is provided.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -38391,6 +39819,11 @@
       <c r="X6" t="inlineStr">
         <is>
           <t>failed: page requires explicit 5-filter selection unless a ciId query param...</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>failed: Current page requires explicit 5-filter selection unless a ciId query param is provided.</t>
         </is>
       </c>
     </row>
@@ -38492,7 +39925,7 @@
       </c>
       <c r="T7" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -38511,6 +39944,11 @@
         </is>
       </c>
       <c r="X7" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -38614,7 +40052,7 @@
       </c>
       <c r="T8" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs a deterministic CI path with at least two seeded skills and task data for both.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a deterministic CI path with at least two seeded skills and task data for both.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -38635,6 +40073,11 @@
       <c r="X8" t="inlineStr">
         <is>
           <t>failed: CI path with at least two seeded skills and task data for both</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>failed: Needs a deterministic CI path with at least two seeded skills and task data for both.</t>
         </is>
       </c>
     </row>
@@ -38736,7 +40179,7 @@
       </c>
       <c r="T9" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs a deterministic task with seeded control points plus a second task for comparison.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a deterministic task with seeded control points plus a second task for comparison.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -38757,6 +40200,11 @@
       <c r="X9" t="inlineStr">
         <is>
           <t>failed: task with seeded control points plus a second task for comparison</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>failed: Needs a deterministic task with seeded control points plus a second task for comparison.</t>
         </is>
       </c>
     </row>
@@ -38858,7 +40306,7 @@
       </c>
       <c r="T10" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs stable seeded rows in all three columns for edit-icon visibility checks.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs stable seeded rows in all three columns for edit-icon visibility checks.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -38879,6 +40327,11 @@
       <c r="X10" t="inlineStr">
         <is>
           <t>failed: stable seeded rows in all three columns for edit-icon visibility ch...</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>failed: Needs stable seeded rows in all three columns for edit-icon visibility checks.</t>
         </is>
       </c>
     </row>
@@ -38980,7 +40433,7 @@
       </c>
       <c r="T11" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -38999,6 +40452,11 @@
         </is>
       </c>
       <c r="X11" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -39093,6 +40551,11 @@
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
         </is>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -39181,6 +40644,11 @@
       <c r="T13" s="13" t="inlineStr">
         <is>
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>not run</t>
         </is>
       </c>
     </row>
@@ -39197,7 +40665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:Y19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="29.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="11.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -39219,6 +40687,8 @@
     <col width="22" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
     <col width="28" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -39342,6 +40812,11 @@
           <t>Test run @ 08:17 PM @ 02/04/26</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Test run @ 11:11 PM @ 03/04/26</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="30.75" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
@@ -39441,7 +40916,7 @@
       </c>
       <c r="T2" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -39460,6 +40935,11 @@
         </is>
       </c>
       <c r="X2" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -39563,7 +41043,7 @@
       </c>
       <c r="T3" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs a deterministic selected skill row under a valid CI path before the edit icon can be asserted reliably.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a deterministic selected skill row under a valid CI path before the edit icon can be asserted reliably.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -39584,6 +41064,11 @@
       <c r="X3" t="inlineStr">
         <is>
           <t>failed: selected skill row under a valid CI path before the edit icon can b...</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>failed: Needs a deterministic selected skill row under a valid CI path before the edit icon can be</t>
         </is>
       </c>
     </row>
@@ -39685,7 +41170,7 @@
       </c>
       <c r="T4" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -39704,6 +41189,11 @@
         </is>
       </c>
       <c r="X4" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -39807,7 +41297,7 @@
       </c>
       <c r="T5" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -39826,6 +41316,11 @@
         </is>
       </c>
       <c r="X5" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -39929,7 +41424,7 @@
       </c>
       <c r="T6" s="13" t="inlineStr">
         <is>
-          <t>Verified passing in the 08:17 PM 02/04/26 rerun.</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -39948,6 +41443,11 @@
         </is>
       </c>
       <c r="X6" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
@@ -40051,7 +41551,7 @@
       </c>
       <c r="T7" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs an existing skill under a valid CI plus stable backend duplicate validation in the current local environment.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs an existing skill under a valid CI plus stable backend duplicate validation in the current local environment.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -40072,6 +41572,11 @@
       <c r="X7" t="inlineStr">
         <is>
           <t>failed: an existing skill under a valid CI plus stable backend duplicate va...</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>failed: Needs an existing skill under a valid CI plus stable backend duplicate validation in the c</t>
         </is>
       </c>
     </row>
@@ -40173,7 +41678,7 @@
       </c>
       <c r="T8" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs an existing skill under a valid CI plus deterministic duplicate validation for trimmed names.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs an existing skill under a valid CI plus deterministic duplicate validation for trimmed names.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -40194,6 +41699,11 @@
       <c r="X8" t="inlineStr">
         <is>
           <t>failed: an existing skill under a valid CI plus deterministic duplicate val...</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>failed: Needs an existing skill under a valid CI plus deterministic duplicate validation for trimm</t>
         </is>
       </c>
     </row>
@@ -40295,7 +41805,7 @@
       </c>
       <c r="T9" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs a valid CI path plus a stable create-panel close path that can be observed in the current local runtime.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a valid CI path plus a stable create-panel close path that can be observed in the current local runtime.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -40316,6 +41826,11 @@
       <c r="X9" t="inlineStr">
         <is>
           <t>failed: a valid CI path plus a stable create-panel close path that can be o...</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>failed: Needs a valid CI path plus a stable create-panel close path that can be observed in the cu</t>
         </is>
       </c>
     </row>
@@ -40417,7 +41932,7 @@
       </c>
       <c r="T10" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs successful skill creation under a valid CI path in the current local environment.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs successful skill creation under a valid CI path in the current local environment.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -40438,6 +41953,11 @@
       <c r="X10" t="inlineStr">
         <is>
           <t>failed: successful skill creation under a valid CI path in the current loca...</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>failed: Needs successful skill creation under a valid CI path in the current local environment.</t>
         </is>
       </c>
     </row>
@@ -40539,7 +42059,7 @@
       </c>
       <c r="T11" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs a deterministic existing skill row and a stable edit path under a valid CI context.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a deterministic existing skill row and a stable edit path under a valid CI context.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -40560,6 +42080,11 @@
       <c r="X11" t="inlineStr">
         <is>
           <t>failed: existing skill row and a stable edit path under a valid CI context</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>failed: Needs a deterministic existing skill row and a stable edit path under a valid CI context.</t>
         </is>
       </c>
     </row>
@@ -40661,7 +42186,7 @@
       </c>
       <c r="T12" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs a deterministic existing skill row plus stable update coverage under a valid CI context.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a deterministic existing skill row plus stable update coverage under a valid CI context.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -40682,6 +42207,11 @@
       <c r="X12" t="inlineStr">
         <is>
           <t>failed: existing skill row plus stable update coverage under a valid CI con...</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>failed: Needs a deterministic existing skill row plus stable update coverage under a valid CI cont</t>
         </is>
       </c>
     </row>
@@ -40783,7 +42313,7 @@
       </c>
       <c r="T13" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs a deterministic existing skill row and stable edit panel access.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a deterministic existing skill row and stable edit panel access.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -40804,6 +42334,11 @@
       <c r="X13" t="inlineStr">
         <is>
           <t>failed: existing skill row and stable edit panel access</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>failed: Needs a deterministic existing skill row and stable edit panel access.</t>
         </is>
       </c>
     </row>
@@ -40905,7 +42440,7 @@
       </c>
       <c r="T14" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs a seeded skill with child tasks plus a stable dependency-block message in the local runtime.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a seeded skill with child tasks plus a stable dependency-block message in the local runtime.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -40926,6 +42461,11 @@
       <c r="X14" t="inlineStr">
         <is>
           <t>failed: a seeded skill with child tasks plus a stable dependency-block mess...</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">failed: Needs a seeded skill with child tasks plus a stable dependency-block message in the local </t>
         </is>
       </c>
     </row>
@@ -41027,7 +42567,7 @@
       </c>
       <c r="T15" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs a childless skill plus stable delete-confirmation behavior under a valid CI context.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a childless skill plus stable delete-confirmation behavior under a valid CI context.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -41048,6 +42588,11 @@
       <c r="X15" t="inlineStr">
         <is>
           <t>failed: a childless skill plus stable delete-confirmation behavior under a...</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>failed: Needs a childless skill plus stable delete-confirmation behavior under a valid CI context.</t>
         </is>
       </c>
     </row>
@@ -41149,7 +42694,7 @@
       </c>
       <c r="T16" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 08:17 PM 02/04/26 rerun: Needs a deterministic existing skill row and stable edit-save coverage under a valid CI context.</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Needs a deterministic existing skill row and stable edit-save coverage under a valid CI context.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -41170,6 +42715,11 @@
       <c r="X16" t="inlineStr">
         <is>
           <t>failed: existing skill row and stable edit-save coverage under a valid CI c...</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>failed: Needs a deterministic existing skill row and stable edit-save coverage under a valid CI co</t>
         </is>
       </c>
     </row>
@@ -41262,6 +42812,11 @@
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
         </is>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -41352,6 +42907,11 @@
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
         </is>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -41440,6 +43000,11 @@
       <c r="T19" s="13" t="inlineStr">
         <is>
           <t>Imported from wrcf-manual-testing.pdf into v2 workbook on 03/04/26; not yet rerun as a workbook case.</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>not run</t>
         </is>
       </c>
     </row>

--- a/temp/WRCF End-to-End Test Cases_reverified-v2.xlsx
+++ b/temp/WRCF End-to-End Test Cases_reverified-v2.xlsx
@@ -9160,7 +9160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:W60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.5703125" customWidth="1" min="1" max="1"/>
@@ -9306,7 +9306,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>COMP-E2E-001</t>
+          <t>COMP-CUR-001</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
@@ -9316,37 +9316,37 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Company dashboard load</t>
+          <t>Manage Company load</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>Verify company WRCF dashboard loads using the referenced industry template</t>
+          <t>Manage Company loads with list and selected company details</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>Authorized Company Admin logged in; company references an industry template</t>
+          <t>Authorized user logged in; at least one company exists</t>
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>Company tenant linked to industry template</t>
+          <t>Existing company record</t>
         </is>
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>1. Open Company WRCF dashboard for a company tenant</t>
+          <t>1. Open Manage Company</t>
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>Company dashboard loads in the context of the referenced industry template</t>
+          <t>Manage Company page loads, list is visible, and selected company details are shown</t>
         </is>
       </c>
       <c r="I2" s="8" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Functional / UI</t>
         </is>
       </c>
       <c r="J2" s="8" t="inlineStr">
@@ -9356,27 +9356,27 @@
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>Company references Industry template</t>
+          <t>Live Manage Company CRUD baseline</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>Company Dashboard</t>
+          <t>Manage Company screen</t>
         </is>
       </c>
       <c r="M2" s="9" t="inlineStr">
         <is>
-          <t>tenants.type='COMPANY' with linked industry/source context</t>
+          <t>List/detail layout</t>
         </is>
       </c>
       <c r="N2" s="8" t="inlineStr">
         <is>
-          <t>Company tenant</t>
+          <t>Login/Auth module</t>
         </is>
       </c>
       <c r="O2" s="14" t="inlineStr">
         <is>
-          <t>@future</t>
+          <t>@stable</t>
         </is>
       </c>
       <c r="P2" s="18" t="inlineStr">
@@ -9391,34 +9391,29 @@
       </c>
       <c r="R2" s="11" t="inlineStr">
         <is>
-          <t>fail</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="S2" s="11" t="inlineStr">
         <is>
-          <t>product-gap</t>
+          <t>none</t>
         </is>
       </c>
       <c r="T2" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live UI at /manage-company is a CRUD management page and does not expose the company WRCF dashboard/template-linked landing surface described in the wor</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>failed: company WRCF dashboard surface missing</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>failed: Current live UI at /manage-company is a CRUD management page and does not expose the compa</t>
+          <t>passed</t>
         </is>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>COMP-E2E-002</t>
+          <t>COMP-CUR-002</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
@@ -9428,32 +9423,32 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>Version summary</t>
+          <t>Company search</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>Verify dashboard shows Industry Version, Company Version, and Overrides count</t>
+          <t>Search filters the company list</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>Company WRCF exists</t>
+          <t>Manage Company loaded with at least one company</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>Industry v4.2, Company v4.2-C1, Overrides=27</t>
+          <t>Search term and unmatched term</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>1. Open Company Dashboard 2. Observe version summary area</t>
+          <t>1. Enter unmatched search 2. Clear search</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>Dashboard shows Industry Version, Company Version, and Overrides count</t>
+          <t>List shows no-result state for unmatched term and restores the list when cleared</t>
         </is>
       </c>
       <c r="I3" s="8" t="inlineStr">
@@ -9463,37 +9458,37 @@
       </c>
       <c r="J3" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K3" s="8" t="inlineStr">
         <is>
-          <t>Company dashboard shows Industry Version, Company Version, Overrides</t>
+          <t>Live Manage Company CRUD baseline</t>
         </is>
       </c>
       <c r="L3" s="8" t="inlineStr">
         <is>
-          <t>Company Dashboard</t>
+          <t>Manage Company screen</t>
         </is>
       </c>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>wrcf_versions + company delta metadata</t>
+          <t>Search behavior</t>
         </is>
       </c>
       <c r="N3" s="8" t="inlineStr">
         <is>
-          <t>Company tenant + versions</t>
+          <t>Company list data</t>
         </is>
       </c>
       <c r="O3" s="14" t="inlineStr">
         <is>
-          <t>@future</t>
+          <t>@stable</t>
         </is>
       </c>
       <c r="P3" s="18" t="inlineStr">
         <is>
-          <t>@p0</t>
+          <t>@p1</t>
         </is>
       </c>
       <c r="Q3" s="22" t="inlineStr">
@@ -9503,34 +9498,29 @@
       </c>
       <c r="R3" s="11" t="inlineStr">
         <is>
-          <t>fail</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="S3" s="11" t="inlineStr">
         <is>
-          <t>product-gap</t>
+          <t>none</t>
         </is>
       </c>
       <c r="T3" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose a company-WRCF version summary area with Industry Version, Company Version, or Overrides count.</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>failed: version summary surface missing</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t xml:space="preserve">failed: Current live Manage Company page does not expose a company-WRCF version summary area with </t>
+          <t>passed</t>
         </is>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>COMP-E2E-003</t>
+          <t>COMP-CUR-003</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
@@ -9540,72 +9530,72 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Dashboard sections</t>
+          <t>Create validation</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Verify dashboard shows Structural Overrides, Capability Overrides, Role Overrides, and Upgrade Available sections when applicable</t>
+          <t>Create form blocks save when Name is empty</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>Company dashboard loaded</t>
+          <t>Manage Company loaded</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>Company with overrides and/or upgrade state</t>
+          <t>Blank name</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>1. Open Company Dashboard 2. Observe visible sections</t>
+          <t>1. Click Add 2. Click Save</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>Dashboard shows Structural Overrides, Capability Overrides, Role Overrides, and Upgrade Available when applicable</t>
+          <t>Validation shows Name is required</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>Functional / UI</t>
+          <t>Functional / Validation</t>
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>Company dashboard sections defined in company WRCF flow</t>
+          <t>Live Manage Company CRUD baseline</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>Company Dashboard</t>
+          <t>Manage Company form</t>
         </is>
       </c>
       <c r="M4" s="9" t="inlineStr">
         <is>
-          <t>Override categories / upgrade state</t>
+          <t>Required-name validation</t>
         </is>
       </c>
       <c r="N4" s="8" t="inlineStr">
         <is>
-          <t>Company tenant</t>
+          <t>Create company form</t>
         </is>
       </c>
       <c r="O4" s="14" t="inlineStr">
         <is>
-          <t>@future</t>
+          <t>@stable</t>
         </is>
       </c>
       <c r="P4" s="18" t="inlineStr">
         <is>
-          <t>@p1</t>
+          <t>@p0</t>
         </is>
       </c>
       <c r="Q4" s="22" t="inlineStr">
@@ -9615,34 +9605,29 @@
       </c>
       <c r="R4" s="11" t="inlineStr">
         <is>
-          <t>fail</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="S4" s="11" t="inlineStr">
         <is>
-          <t>product-gap</t>
+          <t>none</t>
         </is>
       </c>
       <c r="T4" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose company-WRCF override sections or upgrade state sections.</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>failed: override and upgrade sections missing</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>failed: Current live Manage Company page does not expose company-WRCF override sections or upgrade</t>
+          <t>passed</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>COMP-E2E-004</t>
+          <t>COMP-CUR-004</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -9652,72 +9637,72 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Company Admin permissions</t>
+          <t>Edit prefill</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Verify Company Admin can perform override actions only</t>
+          <t>Edit form opens with selected company prefilled</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Company Admin user exists</t>
+          <t>Manage Company loaded with selected company</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Company Admin account</t>
+          <t>Existing selected company</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>1. Login as Company Admin 2. Open company WRCF</t>
+          <t>1. Click Edit</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>User can perform override actions but cannot perform industry-master full-edit actions</t>
+          <t>Edit form opens with selected company values prefilled</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>Role-based / Security</t>
+          <t>Functional / UI</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>Company Admin: Override only</t>
+          <t>Live Manage Company CRUD baseline</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>Company Dashboard / Company Role Adjustments</t>
+          <t>Manage Company form</t>
         </is>
       </c>
       <c r="M5" s="9" t="inlineStr">
         <is>
-          <t>Permissions layer</t>
+          <t>Edit prefill</t>
         </is>
       </c>
       <c r="N5" s="8" t="inlineStr">
         <is>
-          <t>RBAC</t>
+          <t>Selected company detail</t>
         </is>
       </c>
       <c r="O5" s="14" t="inlineStr">
         <is>
-          <t>@future</t>
+          <t>@stable</t>
         </is>
       </c>
       <c r="P5" s="18" t="inlineStr">
         <is>
-          <t>@p0</t>
+          <t>@p1</t>
         </is>
       </c>
       <c r="Q5" s="22" t="inlineStr">
@@ -9727,34 +9712,29 @@
       </c>
       <c r="R5" s="11" t="inlineStr">
         <is>
-          <t>fail</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="S5" s="11" t="inlineStr">
         <is>
-          <t>runtime/data</t>
+          <t>none</t>
         </is>
       </c>
       <c r="T5" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 11:11 PM @ 03/04/26 rerun: This workbook permission case depends on a company-WRCF override surface and a dedicated Company Admin account matrix that are not represented in the current li</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>not run</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>failed: This workbook permission case depends on a company-WRCF override surface and a dedicated C</t>
+          <t>passed</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>COMP-E2E-005</t>
+          <t>COMP-CUR-005</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -9764,72 +9744,72 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Industry Architect permissions</t>
+          <t>Preview flow</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Verify Industry Architect has full edit access to master WRCF flows</t>
+          <t>Preview opens from edit and returns back to list/detail view</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Industry Architect user exists</t>
+          <t>Edit form available for selected company</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Industry Architect account</t>
+          <t>Existing selected company</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>1. Login as Industry Architect 2. Open relevant WRCF context</t>
+          <t>1. Click Edit 2. Click Preview 3. Click Back</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Industry Architect has full edit access to master WRCF flows</t>
+          <t>Preview opens and Back returns to list/detail view</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Role-based / Security</t>
+          <t>Functional / UI</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>Industry Architect: Full edit access</t>
+          <t>Live Manage Company CRUD baseline</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>Industry / Company WRCF views</t>
+          <t>Manage Company preview</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
-          <t>Permissions layer</t>
+          <t>Preview/back flow</t>
         </is>
       </c>
       <c r="N6" s="8" t="inlineStr">
         <is>
-          <t>RBAC</t>
+          <t>Edit form</t>
         </is>
       </c>
       <c r="O6" s="14" t="inlineStr">
         <is>
-          <t>@future</t>
+          <t>@stable</t>
         </is>
       </c>
       <c r="P6" s="18" t="inlineStr">
         <is>
-          <t>@p2</t>
+          <t>@p1</t>
         </is>
       </c>
       <c r="Q6" s="22" t="inlineStr">
@@ -9839,34 +9819,29 @@
       </c>
       <c r="R6" s="11" t="inlineStr">
         <is>
-          <t>fail</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="S6" s="11" t="inlineStr">
         <is>
-          <t>runtime/data</t>
+          <t>none</t>
         </is>
       </c>
       <c r="T6" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 11:11 PM @ 03/04/26 rerun: This workbook permission case targets industry-master WRCF flows rather than the current Manage Company CRUD page and needs dedicated RBAC accounts to verify.</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>not run</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>failed: This workbook permission case targets industry-master WRCF flows rather than the current M</t>
+          <t>passed</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>COMP-E2E-006</t>
+          <t>COMP-CUR-006</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -9876,72 +9851,72 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Auditor permissions</t>
+          <t>Email validation</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Verify Auditor can only view and export company WRCF</t>
+          <t>Contact email format is validated before save</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Auditor user exists</t>
+          <t>Edit form open</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Auditor account</t>
+          <t>Invalid email</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>1. Login as Auditor 2. Open company WRCF</t>
+          <t>1. Open Edit 2. Enter invalid email 3. Click Save</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Company data is viewable/exportable only; override actions are hidden or disabled</t>
+          <t>Validation shows Enter a valid email</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>Role-based / Security</t>
+          <t>Functional / Validation</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>Auditor: View + export only</t>
+          <t>Live Manage Company CRUD baseline</t>
         </is>
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>Company Dashboard</t>
+          <t>Manage Company form</t>
         </is>
       </c>
       <c r="M7" s="9" t="inlineStr">
         <is>
-          <t>Permissions layer</t>
+          <t>Email format validation</t>
         </is>
       </c>
       <c r="N7" s="8" t="inlineStr">
         <is>
-          <t>RBAC</t>
+          <t>Edit form</t>
         </is>
       </c>
       <c r="O7" s="14" t="inlineStr">
         <is>
-          <t>@future</t>
+          <t>@stable</t>
         </is>
       </c>
       <c r="P7" s="18" t="inlineStr">
         <is>
-          <t>@p0</t>
+          <t>@p1</t>
         </is>
       </c>
       <c r="Q7" s="22" t="inlineStr">
@@ -9951,34 +9926,29 @@
       </c>
       <c r="R7" s="11" t="inlineStr">
         <is>
-          <t>fail</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="S7" s="11" t="inlineStr">
         <is>
-          <t>product-gap</t>
+          <t>none</t>
         </is>
       </c>
       <c r="T7" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose the company-WRCF export surface and this role-based case needs a dedicated Auditor account.</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>not run</t>
+          <t>Verified passing in the 11:11 PM @ 03/04/26 rerun.</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t xml:space="preserve">failed: Current live Manage Company page does not expose the company-WRCF export surface and this </t>
+          <t>passed</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>COMP-E2E-007</t>
+          <t>COMP-E2E-001</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -9988,62 +9958,62 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Employee permissions</t>
+          <t>Company dashboard load</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Verify Employee can only view role capability requirements</t>
+          <t>Verify company WRCF dashboard loads using the referenced industry template</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Employee user exists</t>
+          <t>Authorized Company Admin logged in; company references an industry template</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Employee account</t>
+          <t>Company tenant linked to industry template</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>1. Login as Employee 2. Open company role requirement view</t>
+          <t>1. Open Company WRCF dashboard for a company tenant</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Employee can view role capability requirements only and cannot access override actions</t>
+          <t>Company dashboard loads in the context of the referenced industry template</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Role-based / Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>Employee: View role capability requirements only</t>
+          <t>Companies workbook</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t>Company role requirement view</t>
+          <t>Company WRCF dashboard</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr">
         <is>
-          <t>Permissions layer</t>
+          <t>Template-linked company WRCF load</t>
         </is>
       </c>
       <c r="N8" s="8" t="inlineStr">
         <is>
-          <t>RBAC</t>
+          <t>Industry template linkage</t>
         </is>
       </c>
       <c r="O8" s="14" t="inlineStr">
@@ -10053,7 +10023,7 @@
       </c>
       <c r="P8" s="18" t="inlineStr">
         <is>
-          <t>@p1</t>
+          <t>@p0</t>
         </is>
       </c>
       <c r="Q8" s="22" t="inlineStr">
@@ -10073,24 +10043,19 @@
       </c>
       <c r="T8" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live runtime does not expose the company role requirement view described in the workbook and this case needs an Employee account.</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>not run</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live UI at /manage-company is a CRUD management page and does not expose the company WRCF dashboard/template-linked landing surface described in the workbook.</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>failed: Current live runtime does not expose the company role requirement view described in the wo</t>
+          <t>failed: Current live UI at /manage-company is a CRUD management page and does not expose the compa</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>COMP-E2E-008</t>
+          <t>COMP-E2E-002</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -10100,37 +10065,37 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Customize capability instance</t>
+          <t>Version summary</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Verify company can save company-specific capability-instance overrides without duplicating full master data</t>
+          <t>Verify dashboard shows Industry Version, Company Version, and Overrides count</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Company Admin logged in; base industry CI exists</t>
+          <t>Company WRCF exists</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>Master CI plus company override for selected fields</t>
+          <t>Industry v4.2, Company v4.2-C1, Overrides=27</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>1. Open company capability-instance customization 2. Change allowed override fields 3. Save</t>
+          <t>1. Open Company Dashboard 2. Observe version summary area</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>System stores only the company-specific override fields and uses master + override model</t>
+          <t>Dashboard shows Industry Version, Company Version, and Overrides count</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>Functional / Data integrity</t>
+          <t>Functional / UI</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -10140,22 +10105,22 @@
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>Only store company-specific overrides; no duplication explosion</t>
+          <t>Companies workbook</t>
         </is>
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
-          <t>Customize Capability Instance</t>
+          <t>Company WRCF dashboard</t>
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
         <is>
-          <t>Hybrid delta model / override layer</t>
+          <t>Version summary</t>
         </is>
       </c>
       <c r="N9" s="8" t="inlineStr">
         <is>
-          <t>Company tenant + source template CI</t>
+          <t>Company WRCF exists</t>
         </is>
       </c>
       <c r="O9" s="14" t="inlineStr">
@@ -10185,24 +10150,19 @@
       </c>
       <c r="T9" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose company-specific capability-instance override editing or the hybrid master-plus-override save flow.</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>not run</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose a company-WRCF version summary area with Industry Version, Company Version, or Overrides count.</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>failed: Current live Manage Company page does not expose company-specific capability-instance over</t>
+          <t xml:space="preserve">failed: Current live Manage Company page does not expose a company-WRCF version summary area with </t>
         </is>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>COMP-E2E-009</t>
+          <t>COMP-E2E-003</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -10212,62 +10172,62 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Runtime merge view</t>
+          <t>Dashboard sections</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Verify runtime view overlays company overrides on top of the industry master</t>
+          <t>Verify dashboard shows Structural Overrides, Capability Overrides, Role Overrides, and Upgrade Available sections when applicable</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Master template and company override exist</t>
+          <t>Company dashboard loaded</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Master field + overridden field</t>
+          <t>Company with overrides and/or upgrade state</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>1. Load final company WRCF view for overridden context</t>
+          <t>1. Open Company Dashboard 2. Observe visible sections</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>System renders master values together with company override values in the final view</t>
+          <t>Dashboard shows Structural Overrides, Capability Overrides, Role Overrides, and Upgrade Available when applicable</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Functional / Data integrity</t>
+          <t>Functional / UI</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>At runtime, system loads master then overlays company overrides</t>
+          <t>Companies workbook</t>
         </is>
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>Company Dashboard / final rendered view</t>
+          <t>Company WRCF dashboard</t>
         </is>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>Hybrid delta model runtime merge</t>
+          <t>Override sections</t>
         </is>
       </c>
       <c r="N10" s="8" t="inlineStr">
         <is>
-          <t>Company tenant + source template</t>
+          <t>Dashboard loaded</t>
         </is>
       </c>
       <c r="O10" s="14" t="inlineStr">
@@ -10277,7 +10237,7 @@
       </c>
       <c r="P10" s="18" t="inlineStr">
         <is>
-          <t>@p0</t>
+          <t>@p1</t>
         </is>
       </c>
       <c r="Q10" s="22" t="inlineStr">
@@ -10297,24 +10257,19 @@
       </c>
       <c r="T10" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose the final merged company-WRCF runtime view described in the workbook.</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>not run</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose company-WRCF override sections or upgrade state sections.</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>failed: Current live Manage Company page does not expose the final merged company-WRCF runtime vie</t>
+          <t>failed: Current live Manage Company page does not expose company-WRCF override sections or upgrade</t>
         </is>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>COMP-E2E-010</t>
+          <t>COMP-E2E-004</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -10324,62 +10279,62 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Role variant comparison</t>
+          <t>Company Admin permissions</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Verify company role adjustments show Industry Role Template and Company Role Variant</t>
+          <t>Verify Company Admin can perform override actions only</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Company has industry role template and one company role variant</t>
+          <t>Company Admin user exists</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Base role plus company variant</t>
+          <t>Company Admin account</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>1. Open Company Role Adjustments</t>
+          <t>1. Login as Company Admin 2. Open company WRCF</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>System shows Industry Role Template and Company Role Variant comparison</t>
+          <t>User can perform override actions but cannot perform industry-master full-edit actions</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>Functional / UI</t>
+          <t>Role-based / Security</t>
         </is>
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr">
         <is>
-          <t>UI shows Industry Role Template and Company Role Variant</t>
+          <t>Companies workbook</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>Company Role Adjustments</t>
+          <t>Company WRCF RBAC</t>
         </is>
       </c>
       <c r="M11" s="9" t="inlineStr">
         <is>
-          <t>Role override comparison view</t>
+          <t>Company Admin permissions</t>
         </is>
       </c>
       <c r="N11" s="8" t="inlineStr">
         <is>
-          <t>Industry role + company variant</t>
+          <t>Company Admin account</t>
         </is>
       </c>
       <c r="O11" s="14" t="inlineStr">
@@ -10389,7 +10344,7 @@
       </c>
       <c r="P11" s="18" t="inlineStr">
         <is>
-          <t>@p1</t>
+          <t>@p0</t>
         </is>
       </c>
       <c r="Q11" s="22" t="inlineStr">
@@ -10404,29 +10359,24 @@
       </c>
       <c r="S11" s="11" t="inlineStr">
         <is>
-          <t>product-gap</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T11" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose Company Role Adjustments or Industry Role Template vs Company Role Variant comparison.</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>not run</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: This workbook permission case depends on a company-WRCF override surface and a dedicated Company Admin account matrix that are not represented in the current live Manage Company page/runtime.</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>failed: Current live Manage Company page does not expose Company Role Adjustments or Industry Role</t>
+          <t>failed: This workbook permission case depends on a company-WRCF override surface and a dedicated C</t>
         </is>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>COMP-E2E-011</t>
+          <t>COMP-E2E-005</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -10436,62 +10386,62 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Role variant color coding</t>
+          <t>Industry Architect permissions</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Verify comparison uses color coding for same, overridden, and removed items</t>
+          <t>Verify Industry Architect has full edit access to master WRCF flows</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Comparison screen open</t>
+          <t>Industry Architect user exists</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>Mixed same/overridden/removed items</t>
+          <t>Industry Architect account</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>1. Open role comparison screen 2. Observe status colors</t>
+          <t>1. Login as Industry Architect 2. Open relevant WRCF context</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Green marks same as industry, Orange marks overridden, and Red marks removed</t>
+          <t>Industry Architect has full edit access to master WRCF flows</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>UI / Requirement validation</t>
+          <t>Role-based / Security</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
-          <t>Color coding: Green same, Orange overridden, Red removed</t>
+          <t>Companies workbook</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>Company Role Adjustments</t>
+          <t>WRCF RBAC</t>
         </is>
       </c>
       <c r="M12" s="9" t="inlineStr">
         <is>
-          <t>Comparison-state rendering</t>
+          <t>Industry Architect permissions</t>
         </is>
       </c>
       <c r="N12" s="8" t="inlineStr">
         <is>
-          <t>Industry role + company variant</t>
+          <t>Industry Architect account</t>
         </is>
       </c>
       <c r="O12" s="14" t="inlineStr">
@@ -10516,29 +10466,24 @@
       </c>
       <c r="S12" s="11" t="inlineStr">
         <is>
-          <t>product-gap</t>
+          <t>runtime/data</t>
         </is>
       </c>
       <c r="T12" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose the workbook role-comparison screen needed for this color-coding validation.</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>not run</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: This workbook permission case targets industry-master WRCF flows rather than the current Manage Company CRUD page and needs dedicated RBAC accounts to verify.</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>failed: Current live Manage Company page does not expose the workbook role-comparison screen neede</t>
+          <t>failed: This workbook permission case targets industry-master WRCF flows rather than the current M</t>
         </is>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>COMP-E2E-012</t>
+          <t>COMP-E2E-006</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -10548,62 +10493,62 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Add internal company role</t>
+          <t>Auditor permissions</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Verify company can add a new internal role</t>
+          <t>Verify Auditor can only view and export company WRCF</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Company Admin logged in</t>
+          <t>Auditor user exists</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>Unique internal role name</t>
+          <t>Auditor account</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>1. Open Company Role Adjustments 2. Add new internal role 3. Save</t>
+          <t>1. Login as Auditor 2. Open company WRCF</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>New internal company role is added to the company variant</t>
+          <t>Company data is viewable/exportable only; override actions are hidden or disabled</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Role-based / Security</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>Company can add new internal roles</t>
+          <t>Companies workbook</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>Company Role Adjustments</t>
+          <t>Company WRCF RBAC</t>
         </is>
       </c>
       <c r="M13" s="9" t="inlineStr">
         <is>
-          <t>Company role override layer</t>
+          <t>Auditor permissions</t>
         </is>
       </c>
       <c r="N13" s="8" t="inlineStr">
         <is>
-          <t>Company tenant</t>
+          <t>Auditor account</t>
         </is>
       </c>
       <c r="O13" s="14" t="inlineStr">
@@ -10613,7 +10558,7 @@
       </c>
       <c r="P13" s="18" t="inlineStr">
         <is>
-          <t>@p1</t>
+          <t>@p0</t>
         </is>
       </c>
       <c r="Q13" s="22" t="inlineStr">
@@ -10633,24 +10578,19 @@
       </c>
       <c r="T13" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose the company role-variant creation surface described in the workbook.</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>not run</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose the company-WRCF export surface and this role-based case needs a dedicated Auditor account.</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>failed: Current live Manage Company page does not expose the company role-variant creation surface</t>
+          <t xml:space="preserve">failed: Current live Manage Company page does not expose the company-WRCF export surface and this </t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>COMP-E2E-013</t>
+          <t>COMP-E2E-007</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
@@ -10660,37 +10600,37 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Adjust capability weight</t>
+          <t>Employee permissions</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Verify company can adjust capability weights in the company role variant</t>
+          <t>Verify Employee can only view role capability requirements</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Company role variant exists</t>
+          <t>Employee user exists</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>Changed weight for one mapped CI</t>
+          <t>Employee account</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>1. Open a company role variant 2. Adjust capability weight 3. Save</t>
+          <t>1. Login as Employee 2. Open company role requirement view</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>Updated capability weight is saved in the company role variant</t>
+          <t>Employee can view role capability requirements only and cannot access override actions</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Role-based / Security</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
@@ -10700,22 +10640,22 @@
       </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>Company can adjust capability weights</t>
+          <t>Companies workbook</t>
         </is>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>Company Role Adjustments</t>
+          <t>Company WRCF RBAC</t>
         </is>
       </c>
       <c r="M14" s="9" t="inlineStr">
         <is>
-          <t>Company override on role mapping weight</t>
+          <t>Employee permissions</t>
         </is>
       </c>
       <c r="N14" s="8" t="inlineStr">
         <is>
-          <t>Company role variant</t>
+          <t>Employee account</t>
         </is>
       </c>
       <c r="O14" s="14" t="inlineStr">
@@ -10745,24 +10685,19 @@
       </c>
       <c r="T14" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose company role-variant capability weight adjustment.</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>not run</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live runtime does not expose the company role requirement view described in the workbook and this case needs an Employee account.</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>failed: Current live Manage Company page does not expose company role-variant capability weight ad</t>
+          <t>failed: Current live runtime does not expose the company role requirement view described in the wo</t>
         </is>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>COMP-E2E-014</t>
+          <t>COMP-E2E-008</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -10772,62 +10707,62 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Change certification threshold</t>
+          <t>Customize capability instance</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Verify company can change certification threshold in the company role variant</t>
+          <t>Verify company can save company-specific capability-instance overrides without duplicating full master data</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Company role variant exists</t>
+          <t>Company Admin logged in; base industry CI exists</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>New threshold value</t>
+          <t>Master CI plus company override for selected fields</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>1. Open company role variant 2. Change certification threshold 3. Save</t>
+          <t>1. Open company capability-instance customization 2. Change allowed override fields 3. Save</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>Updated certification threshold is saved in the company role variant</t>
+          <t>System stores only the company-specific override fields and uses master + override model</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Functional / Data integrity</t>
         </is>
       </c>
       <c r="J15" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>Company can change certification threshold</t>
+          <t>Companies workbook</t>
         </is>
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>Company Role Adjustments</t>
+          <t>Company capability override</t>
         </is>
       </c>
       <c r="M15" s="9" t="inlineStr">
         <is>
-          <t>Company role variant threshold override</t>
+          <t>Override save model</t>
         </is>
       </c>
       <c r="N15" s="8" t="inlineStr">
         <is>
-          <t>Company role variant</t>
+          <t>Base industry CI exists</t>
         </is>
       </c>
       <c r="O15" s="14" t="inlineStr">
@@ -10837,7 +10772,7 @@
       </c>
       <c r="P15" s="18" t="inlineStr">
         <is>
-          <t>@p1</t>
+          <t>@p0</t>
         </is>
       </c>
       <c r="Q15" s="22" t="inlineStr">
@@ -10857,24 +10792,19 @@
       </c>
       <c r="T15" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose company role-variant certification-threshold override editing.</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>not run</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose company-specific capability-instance override editing or the hybrid master-plus-override save flow.</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>failed: Current live Manage Company page does not expose company role-variant certification-thresh</t>
+          <t>failed: Current live Manage Company page does not expose company-specific capability-instance over</t>
         </is>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>COMP-E2E-015</t>
+          <t>COMP-E2E-009</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -10884,37 +10814,37 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Upgrade available indicator</t>
+          <t>Runtime merge view</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Verify company sees Upgrade Available when industry publishes a newer version</t>
+          <t>Verify runtime view overlays company overrides on top of the industry master</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Company references industry version 4.2; industry publishes 5.0</t>
+          <t>Master template and company override exist</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>Newer published industry version available</t>
+          <t>Master field + overridden field</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>1. Publish newer industry version 2. Open company dashboard</t>
+          <t>1. Load final company WRCF view for overridden context</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>Dashboard shows Upgrade Available with the newer industry version</t>
+          <t>System renders master values together with company override values in the final view</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>Functional / Versioning</t>
+          <t>Functional / Data integrity</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -10924,22 +10854,22 @@
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>When Industry updates, companies get Upgrade Available</t>
+          <t>Companies workbook</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>Company Dashboard</t>
+          <t>Company merged runtime view</t>
         </is>
       </c>
       <c r="M16" s="9" t="inlineStr">
         <is>
-          <t>Industry/company version comparison</t>
+          <t>Master + override overlay</t>
         </is>
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>Industry version + company version</t>
+          <t>Master and company override</t>
         </is>
       </c>
       <c r="O16" s="14" t="inlineStr">
@@ -10969,24 +10899,19 @@
       </c>
       <c r="T16" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose industry/company WRCF version comparison or Upgrade Available state.</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>not run</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose the final merged company-WRCF runtime view described in the workbook.</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t xml:space="preserve">failed: Current live Manage Company page does not expose industry/company WRCF version comparison </t>
+          <t>failed: Current live Manage Company page does not expose the final merged company-WRCF runtime vie</t>
         </is>
       </c>
     </row>
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>COMP-E2E-016</t>
+          <t>COMP-E2E-010</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -10996,62 +10921,62 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Upgrade diff screen</t>
+          <t>Role variant comparison</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Verify upgrade flow shows diffs before applying update</t>
+          <t>Verify company role adjustments show Industry Role Template and Company Role Variant</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Upgrade available state exists</t>
+          <t>Company has industry role template and one company role variant</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>Changes include new CI / modified escalation / updated regulatory refs</t>
+          <t>Base role plus company variant</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>1. Open Upgrade Available 2. Review diff screen</t>
+          <t>1. Open Company Role Adjustments</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>System shows differences such as new capability instances, modified escalation levels, and updated regulatory references</t>
+          <t>System shows Industry Role Template and Company Role Variant comparison</t>
         </is>
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>Functional / Versioning</t>
+          <t>Functional / UI</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>Upgrade &amp; Merge Flow shows diff before decision</t>
+          <t>Companies workbook</t>
         </is>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>Upgrade &amp; Merge Flow</t>
+          <t>Company role adjustments</t>
         </is>
       </c>
       <c r="M17" s="9" t="inlineStr">
         <is>
-          <t>Diff against source template version</t>
+          <t>Role template vs variant</t>
         </is>
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>Industry version delta</t>
+          <t>Company role variant exists</t>
         </is>
       </c>
       <c r="O17" s="14" t="inlineStr">
@@ -11061,7 +10986,7 @@
       </c>
       <c r="P17" s="18" t="inlineStr">
         <is>
-          <t>@p0</t>
+          <t>@p1</t>
         </is>
       </c>
       <c r="Q17" s="22" t="inlineStr">
@@ -11081,24 +11006,19 @@
       </c>
       <c r="T17" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose the workbook Upgrade &amp; Merge diff flow.</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>not run</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose Company Role Adjustments or Industry Role Template vs Company Role Variant comparison.</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>failed: Current live Manage Company page does not expose the workbook Upgrade &amp; Merge diff flow.</t>
+          <t>failed: Current live Manage Company page does not expose Company Role Adjustments or Industry Role</t>
         </is>
       </c>
     </row>
     <row r="18" ht="60" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>COMP-E2E-017</t>
+          <t>COMP-E2E-011</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -11108,62 +11028,62 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Accept all upgrade</t>
+          <t>Role variant color coding</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Verify Accept All applies all industry updates and generates the next company version</t>
+          <t>Verify comparison uses color coding for same, overridden, and removed items</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Upgrade available state exists</t>
+          <t>Comparison screen open</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>Company on 4.2-C1; industry on 5.0</t>
+          <t>Mixed same/overridden/removed items</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>1. Open upgrade flow 2. Click Accept All 3. Confirm</t>
+          <t>1. Open role comparison screen 2. Observe status colors</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>All applicable updates are applied and a new company version is generated</t>
+          <t>Green marks same as industry, Orange marks overridden, and Red marks removed</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>Functional / Versioning</t>
+          <t>UI / Requirement validation</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>Final step generates next company version after accepted updates</t>
+          <t>Companies workbook</t>
         </is>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>Upgrade &amp; Merge Flow</t>
+          <t>Company role comparison</t>
         </is>
       </c>
       <c r="M18" s="9" t="inlineStr">
         <is>
-          <t>Company version generation after merge</t>
+          <t>Color coding</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>Industry version delta + company version</t>
+          <t>Comparison screen open</t>
         </is>
       </c>
       <c r="O18" s="14" t="inlineStr">
@@ -11173,7 +11093,7 @@
       </c>
       <c r="P18" s="18" t="inlineStr">
         <is>
-          <t>@p0</t>
+          <t>@p1</t>
         </is>
       </c>
       <c r="Q18" s="22" t="inlineStr">
@@ -11193,24 +11113,19 @@
       </c>
       <c r="T18" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose the workbook Upgrade &amp; Merge accept-all flow or company version generation.</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>not run</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose the workbook role-comparison screen needed for this color-coding validation.</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>failed: Current live Manage Company page does not expose the workbook Upgrade &amp; Merge accept-all f</t>
+          <t>failed: Current live Manage Company page does not expose the workbook role-comparison screen neede</t>
         </is>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>COMP-E2E-018</t>
+          <t>COMP-E2E-012</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -11220,62 +11135,62 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Review individually</t>
+          <t>Add internal company role</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Verify Review Individually allows accepting some changes and keeping current for others</t>
+          <t>Verify company can add a new internal role</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Upgrade diff screen open</t>
+          <t>Company Admin logged in</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>Mixed changes in upgrade diff</t>
+          <t>Unique internal role name</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>1. Open Review Individually 2. Accept one change 3. Keep Current for another 4. Save</t>
+          <t>1. Open Company Role Adjustments 2. Add new internal role 3. Save</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>System applies only accepted changes and preserves current values for kept items</t>
+          <t>New internal company role is added to the company variant</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>Functional / Versioning</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>Each change has [Accept] [Keep Current]</t>
+          <t>Companies workbook</t>
         </is>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>Upgrade &amp; Merge Flow</t>
+          <t>Company role adjustments</t>
         </is>
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
-          <t>Selective merge of company overrides</t>
+          <t>Add internal role</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>Industry version delta + company overrides</t>
+          <t>Company Admin logged in</t>
         </is>
       </c>
       <c r="O19" s="14" t="inlineStr">
@@ -11285,7 +11200,7 @@
       </c>
       <c r="P19" s="18" t="inlineStr">
         <is>
-          <t>@p0</t>
+          <t>@p1</t>
         </is>
       </c>
       <c r="Q19" s="22" t="inlineStr">
@@ -11305,24 +11220,19 @@
       </c>
       <c r="T19" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose the workbook selective upgrade-merge decision flow.</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>not run</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose the company role-variant creation surface described in the workbook.</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>failed: Current live Manage Company page does not expose the workbook selective upgrade-merge deci</t>
+          <t>failed: Current live Manage Company page does not expose the company role-variant creation surface</t>
         </is>
       </c>
     </row>
     <row r="20" ht="60" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>COMP-E2E-019</t>
+          <t>COMP-E2E-013</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -11332,37 +11242,37 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Defer upgrade</t>
+          <t>Adjust capability weight</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Verify company can defer an upgrade without changing the current company version</t>
+          <t>Verify company can adjust capability weights in the company role variant</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Upgrade available state exists</t>
+          <t>Company role variant exists</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>Company on old version with newer source version available</t>
+          <t>Changed weight for one mapped CI</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>1. Open upgrade flow 2. Click Defer Upgrade</t>
+          <t>1. Open a company role variant 2. Adjust capability weight 3. Save</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>Current company version remains unchanged and upgrade remains pending/available</t>
+          <t>Updated capability weight is saved in the company role variant</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>Functional / Versioning</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
@@ -11372,22 +11282,22 @@
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>Company option includes Defer Upgrade</t>
+          <t>Companies workbook</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>Upgrade &amp; Merge Flow</t>
+          <t>Company role adjustments</t>
         </is>
       </c>
       <c r="M20" s="9" t="inlineStr">
         <is>
-          <t>No version change on defer</t>
+          <t>Capability weight change</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>Industry version delta + company version</t>
+          <t>Company role variant exists</t>
         </is>
       </c>
       <c r="O20" s="14" t="inlineStr">
@@ -11417,61 +11327,1404 @@
       </c>
       <c r="T20" s="13" t="inlineStr">
         <is>
-          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose the workbook Defer Upgrade flow or company-WRCF version state.</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>not run</t>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose company role-variant capability weight adjustment.</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>failed: Current live Manage Company page does not expose the workbook Defer Upgrade flow or compan</t>
+          <t>failed: Current live Manage Company page does not expose company role-variant capability weight ad</t>
         </is>
       </c>
     </row>
     <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="8" t="n"/>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="8" t="n"/>
-      <c r="J21" s="8" t="n"/>
-      <c r="K21" s="8" t="n"/>
-      <c r="L21" s="8" t="n"/>
-      <c r="M21" s="9" t="n"/>
-      <c r="N21" s="8" t="n"/>
-      <c r="R21" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>COMP-E2E-014</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Companies</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Change certification threshold</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Verify company can change certification threshold in the company role variant</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Company role variant exists</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>New threshold value</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>1. Open company role variant 2. Change certification threshold 3. Save</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>Updated certification threshold is saved in the company role variant</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>Companies workbook</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>Company role adjustments</t>
+        </is>
+      </c>
+      <c r="M21" s="9" t="inlineStr">
+        <is>
+          <t>Certification threshold change</t>
+        </is>
+      </c>
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t>Company role variant exists</t>
+        </is>
+      </c>
+      <c r="O21" s="14" t="inlineStr">
+        <is>
+          <t>@future</t>
+        </is>
+      </c>
+      <c r="P21" s="18" t="inlineStr">
+        <is>
+          <t>@p1</t>
+        </is>
+      </c>
+      <c r="Q21" s="22" t="inlineStr">
+        <is>
+          <t>@companies</t>
+        </is>
+      </c>
+      <c r="R21" s="11" t="inlineStr">
         <is>
           <t>fail</t>
+        </is>
+      </c>
+      <c r="S21" s="11" t="inlineStr">
+        <is>
+          <t>product-gap</t>
+        </is>
+      </c>
+      <c r="T21" s="13" t="inlineStr">
+        <is>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose company role-variant certification-threshold override editing.</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>failed: Current live Manage Company page does not expose company role-variant certification-thresh</t>
         </is>
       </c>
     </row>
     <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="8" t="n"/>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
-      <c r="J22" s="8" t="n"/>
-      <c r="K22" s="8" t="n"/>
-      <c r="L22" s="8" t="n"/>
-      <c r="M22" s="9" t="n"/>
-      <c r="N22" s="8" t="n"/>
-      <c r="R22" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>COMP-E2E-015</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Companies</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Upgrade available indicator</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Verify company sees Upgrade Available when industry publishes a newer version</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>Company references industry version 4.2; industry publishes 5.0</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Newer published industry version available</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>1. Publish newer industry version 2. Open company dashboard</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>Dashboard shows Upgrade Available with the newer industry version</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>Functional / Versioning</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>Companies workbook</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>Company upgrade flow</t>
+        </is>
+      </c>
+      <c r="M22" s="9" t="inlineStr">
+        <is>
+          <t>Upgrade Available</t>
+        </is>
+      </c>
+      <c r="N22" s="8" t="inlineStr">
+        <is>
+          <t>Newer industry version</t>
+        </is>
+      </c>
+      <c r="O22" s="14" t="inlineStr">
+        <is>
+          <t>@future</t>
+        </is>
+      </c>
+      <c r="P22" s="18" t="inlineStr">
+        <is>
+          <t>@p0</t>
+        </is>
+      </c>
+      <c r="Q22" s="22" t="inlineStr">
+        <is>
+          <t>@companies</t>
+        </is>
+      </c>
+      <c r="R22" s="11" t="inlineStr">
         <is>
           <t>fail</t>
         </is>
       </c>
+      <c r="S22" s="11" t="inlineStr">
+        <is>
+          <t>product-gap</t>
+        </is>
+      </c>
+      <c r="T22" s="13" t="inlineStr">
+        <is>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose industry/company WRCF version comparison or Upgrade Available state.</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">failed: Current live Manage Company page does not expose industry/company WRCF version comparison </t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>COMP-E2E-016</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Companies</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Upgrade diff screen</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Verify upgrade flow shows diffs before applying update</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>Upgrade available state exists</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Changes include new CI / modified escalation / updated regulatory refs</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>1. Open Upgrade Available 2. Review diff screen</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>System shows differences such as new capability instances, modified escalation levels, and updated regulatory references</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>Functional / Versioning</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>Companies workbook</t>
+        </is>
+      </c>
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <t>Company upgrade flow</t>
+        </is>
+      </c>
+      <c r="M23" s="9" t="inlineStr">
+        <is>
+          <t>Upgrade diff screen</t>
+        </is>
+      </c>
+      <c r="N23" s="8" t="inlineStr">
+        <is>
+          <t>Upgrade available state</t>
+        </is>
+      </c>
+      <c r="O23" s="14" t="inlineStr">
+        <is>
+          <t>@future</t>
+        </is>
+      </c>
+      <c r="P23" s="18" t="inlineStr">
+        <is>
+          <t>@p0</t>
+        </is>
+      </c>
+      <c r="Q23" s="22" t="inlineStr">
+        <is>
+          <t>@companies</t>
+        </is>
+      </c>
+      <c r="R23" s="11" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="S23" s="11" t="inlineStr">
+        <is>
+          <t>product-gap</t>
+        </is>
+      </c>
+      <c r="T23" s="13" t="inlineStr">
+        <is>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose the workbook Upgrade &amp; Merge diff flow.</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>failed: Current live Manage Company page does not expose the workbook Upgrade &amp; Merge diff flow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>COMP-E2E-017</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Companies</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Accept all upgrade</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Verify Accept All applies all industry updates and generates the next company version</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Upgrade available state exists</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Company on 4.2-C1; industry on 5.0</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>1. Open upgrade flow 2. Click Accept All 3. Confirm</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>All applicable updates are applied and a new company version is generated</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>Functional / Versioning</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>Companies workbook</t>
+        </is>
+      </c>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>Company upgrade flow</t>
+        </is>
+      </c>
+      <c r="M24" s="9" t="inlineStr">
+        <is>
+          <t>Accept all upgrade</t>
+        </is>
+      </c>
+      <c r="N24" s="8" t="inlineStr">
+        <is>
+          <t>Upgrade available state</t>
+        </is>
+      </c>
+      <c r="O24" s="14" t="inlineStr">
+        <is>
+          <t>@future</t>
+        </is>
+      </c>
+      <c r="P24" s="18" t="inlineStr">
+        <is>
+          <t>@p0</t>
+        </is>
+      </c>
+      <c r="Q24" s="22" t="inlineStr">
+        <is>
+          <t>@companies</t>
+        </is>
+      </c>
+      <c r="R24" s="11" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="S24" s="11" t="inlineStr">
+        <is>
+          <t>product-gap</t>
+        </is>
+      </c>
+      <c r="T24" s="13" t="inlineStr">
+        <is>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose the workbook Upgrade &amp; Merge accept-all flow or company version generation.</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>failed: Current live Manage Company page does not expose the workbook Upgrade &amp; Merge accept-all f</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>COMP-E2E-018</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Companies</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Review individually</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Verify Review Individually allows accepting some changes and keeping current for others</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>Upgrade diff screen open</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Mixed changes in upgrade diff</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>1. Open Review Individually 2. Accept one change 3. Keep Current for another 4. Save</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>System applies only accepted changes and preserves current values for kept items</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>Functional / Versioning</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>Companies workbook</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>Company upgrade flow</t>
+        </is>
+      </c>
+      <c r="M25" s="9" t="inlineStr">
+        <is>
+          <t>Review individually</t>
+        </is>
+      </c>
+      <c r="N25" s="8" t="inlineStr">
+        <is>
+          <t>Upgrade diff screen open</t>
+        </is>
+      </c>
+      <c r="O25" s="14" t="inlineStr">
+        <is>
+          <t>@future</t>
+        </is>
+      </c>
+      <c r="P25" s="18" t="inlineStr">
+        <is>
+          <t>@p0</t>
+        </is>
+      </c>
+      <c r="Q25" s="22" t="inlineStr">
+        <is>
+          <t>@companies</t>
+        </is>
+      </c>
+      <c r="R25" s="11" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="S25" s="11" t="inlineStr">
+        <is>
+          <t>product-gap</t>
+        </is>
+      </c>
+      <c r="T25" s="13" t="inlineStr">
+        <is>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose the workbook selective upgrade-merge decision flow.</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>failed: Current live Manage Company page does not expose the workbook selective upgrade-merge deci</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>COMP-E2E-019</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Companies</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Defer upgrade</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Verify company can defer an upgrade without changing the current company version</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>Upgrade available state exists</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Company on old version with newer source version available</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>1. Open upgrade flow 2. Click Defer Upgrade</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>Current company version remains unchanged and upgrade remains pending/available</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>Functional / Versioning</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>Companies workbook</t>
+        </is>
+      </c>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>Company upgrade flow</t>
+        </is>
+      </c>
+      <c r="M26" s="9" t="inlineStr">
+        <is>
+          <t>Defer upgrade</t>
+        </is>
+      </c>
+      <c r="N26" s="8" t="inlineStr">
+        <is>
+          <t>Upgrade available state</t>
+        </is>
+      </c>
+      <c r="O26" s="14" t="inlineStr">
+        <is>
+          <t>@future</t>
+        </is>
+      </c>
+      <c r="P26" s="18" t="inlineStr">
+        <is>
+          <t>@p1</t>
+        </is>
+      </c>
+      <c r="Q26" s="22" t="inlineStr">
+        <is>
+          <t>@companies</t>
+        </is>
+      </c>
+      <c r="R26" s="11" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="S26" s="11" t="inlineStr">
+        <is>
+          <t>product-gap</t>
+        </is>
+      </c>
+      <c r="T26" s="13" t="inlineStr">
+        <is>
+          <t>Failed in the 11:11 PM @ 03/04/26 rerun: Current live Manage Company page does not expose the workbook Defer Upgrade flow or company-WRCF version state.</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>failed: Current live Manage Company page does not expose the workbook Defer Upgrade flow or compan</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="n"/>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="8" t="n"/>
+      <c r="H27" s="8" t="n"/>
+      <c r="I27" s="8" t="n"/>
+      <c r="J27" s="8" t="n"/>
+      <c r="K27" s="8" t="n"/>
+      <c r="L27" s="8" t="n"/>
+      <c r="M27" s="9" t="n"/>
+      <c r="N27" s="8" t="n"/>
+      <c r="O27" s="14" t="n"/>
+      <c r="P27" s="18" t="n"/>
+      <c r="Q27" s="22" t="n"/>
+      <c r="R27" s="11" t="n"/>
+      <c r="S27" s="11" t="n"/>
+      <c r="T27" s="13" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="n"/>
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="8" t="n"/>
+      <c r="J28" s="8" t="n"/>
+      <c r="K28" s="8" t="n"/>
+      <c r="L28" s="8" t="n"/>
+      <c r="M28" s="9" t="n"/>
+      <c r="N28" s="8" t="n"/>
+      <c r="O28" s="14" t="n"/>
+      <c r="P28" s="18" t="n"/>
+      <c r="Q28" s="22" t="n"/>
+      <c r="R28" s="11" t="n"/>
+      <c r="S28" s="11" t="n"/>
+      <c r="T28" s="13" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="n"/>
+      <c r="B29" s="8" t="n"/>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="8" t="n"/>
+      <c r="H29" s="8" t="n"/>
+      <c r="I29" s="8" t="n"/>
+      <c r="J29" s="8" t="n"/>
+      <c r="K29" s="8" t="n"/>
+      <c r="L29" s="8" t="n"/>
+      <c r="M29" s="9" t="n"/>
+      <c r="N29" s="8" t="n"/>
+      <c r="O29" s="14" t="n"/>
+      <c r="P29" s="18" t="n"/>
+      <c r="Q29" s="22" t="n"/>
+      <c r="R29" s="11" t="n"/>
+      <c r="S29" s="11" t="n"/>
+      <c r="T29" s="13" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="8" t="n"/>
+      <c r="H30" s="8" t="n"/>
+      <c r="I30" s="8" t="n"/>
+      <c r="J30" s="8" t="n"/>
+      <c r="K30" s="8" t="n"/>
+      <c r="L30" s="8" t="n"/>
+      <c r="M30" s="9" t="n"/>
+      <c r="N30" s="8" t="n"/>
+      <c r="O30" s="14" t="n"/>
+      <c r="P30" s="18" t="n"/>
+      <c r="Q30" s="22" t="n"/>
+      <c r="R30" s="11" t="n"/>
+      <c r="S30" s="11" t="n"/>
+      <c r="T30" s="13" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="n"/>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="8" t="n"/>
+      <c r="G31" s="8" t="n"/>
+      <c r="H31" s="8" t="n"/>
+      <c r="I31" s="8" t="n"/>
+      <c r="J31" s="8" t="n"/>
+      <c r="K31" s="8" t="n"/>
+      <c r="L31" s="8" t="n"/>
+      <c r="M31" s="9" t="n"/>
+      <c r="N31" s="8" t="n"/>
+      <c r="O31" s="14" t="n"/>
+      <c r="P31" s="18" t="n"/>
+      <c r="Q31" s="22" t="n"/>
+      <c r="R31" s="11" t="n"/>
+      <c r="S31" s="11" t="n"/>
+      <c r="T31" s="13" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n"/>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="8" t="n"/>
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="8" t="n"/>
+      <c r="J32" s="8" t="n"/>
+      <c r="K32" s="8" t="n"/>
+      <c r="L32" s="8" t="n"/>
+      <c r="M32" s="9" t="n"/>
+      <c r="N32" s="8" t="n"/>
+      <c r="O32" s="14" t="n"/>
+      <c r="P32" s="18" t="n"/>
+      <c r="Q32" s="22" t="n"/>
+      <c r="R32" s="11" t="n"/>
+      <c r="S32" s="11" t="n"/>
+      <c r="T32" s="13" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="n"/>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="8" t="n"/>
+      <c r="F33" s="8" t="n"/>
+      <c r="G33" s="8" t="n"/>
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="8" t="n"/>
+      <c r="J33" s="8" t="n"/>
+      <c r="K33" s="8" t="n"/>
+      <c r="L33" s="8" t="n"/>
+      <c r="M33" s="9" t="n"/>
+      <c r="N33" s="8" t="n"/>
+      <c r="O33" s="14" t="n"/>
+      <c r="P33" s="18" t="n"/>
+      <c r="Q33" s="22" t="n"/>
+      <c r="R33" s="11" t="n"/>
+      <c r="S33" s="11" t="n"/>
+      <c r="T33" s="13" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+      <c r="G34" s="8" t="n"/>
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="8" t="n"/>
+      <c r="J34" s="8" t="n"/>
+      <c r="K34" s="8" t="n"/>
+      <c r="L34" s="8" t="n"/>
+      <c r="M34" s="9" t="n"/>
+      <c r="N34" s="8" t="n"/>
+      <c r="O34" s="14" t="n"/>
+      <c r="P34" s="18" t="n"/>
+      <c r="Q34" s="22" t="n"/>
+      <c r="R34" s="11" t="n"/>
+      <c r="S34" s="11" t="n"/>
+      <c r="T34" s="13" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="n"/>
+      <c r="B35" s="8" t="n"/>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="8" t="n"/>
+      <c r="F35" s="8" t="n"/>
+      <c r="G35" s="8" t="n"/>
+      <c r="H35" s="8" t="n"/>
+      <c r="I35" s="8" t="n"/>
+      <c r="J35" s="8" t="n"/>
+      <c r="K35" s="8" t="n"/>
+      <c r="L35" s="8" t="n"/>
+      <c r="M35" s="9" t="n"/>
+      <c r="N35" s="8" t="n"/>
+      <c r="O35" s="14" t="n"/>
+      <c r="P35" s="18" t="n"/>
+      <c r="Q35" s="22" t="n"/>
+      <c r="R35" s="11" t="n"/>
+      <c r="S35" s="11" t="n"/>
+      <c r="T35" s="13" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n"/>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="8" t="n"/>
+      <c r="G36" s="8" t="n"/>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="8" t="n"/>
+      <c r="J36" s="8" t="n"/>
+      <c r="K36" s="8" t="n"/>
+      <c r="L36" s="8" t="n"/>
+      <c r="M36" s="9" t="n"/>
+      <c r="N36" s="8" t="n"/>
+      <c r="O36" s="14" t="n"/>
+      <c r="P36" s="18" t="n"/>
+      <c r="Q36" s="22" t="n"/>
+      <c r="R36" s="11" t="n"/>
+      <c r="S36" s="11" t="n"/>
+      <c r="T36" s="13" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="n"/>
+      <c r="B37" s="8" t="n"/>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="8" t="n"/>
+      <c r="F37" s="8" t="n"/>
+      <c r="G37" s="8" t="n"/>
+      <c r="H37" s="8" t="n"/>
+      <c r="I37" s="8" t="n"/>
+      <c r="J37" s="8" t="n"/>
+      <c r="K37" s="8" t="n"/>
+      <c r="L37" s="8" t="n"/>
+      <c r="M37" s="9" t="n"/>
+      <c r="N37" s="8" t="n"/>
+      <c r="O37" s="14" t="n"/>
+      <c r="P37" s="18" t="n"/>
+      <c r="Q37" s="22" t="n"/>
+      <c r="R37" s="11" t="n"/>
+      <c r="S37" s="11" t="n"/>
+      <c r="T37" s="13" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n"/>
+      <c r="B38" s="8" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="8" t="n"/>
+      <c r="G38" s="8" t="n"/>
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="8" t="n"/>
+      <c r="J38" s="8" t="n"/>
+      <c r="K38" s="8" t="n"/>
+      <c r="L38" s="8" t="n"/>
+      <c r="M38" s="9" t="n"/>
+      <c r="N38" s="8" t="n"/>
+      <c r="O38" s="14" t="n"/>
+      <c r="P38" s="18" t="n"/>
+      <c r="Q38" s="22" t="n"/>
+      <c r="R38" s="11" t="n"/>
+      <c r="S38" s="11" t="n"/>
+      <c r="T38" s="13" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="n"/>
+      <c r="B39" s="8" t="n"/>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="8" t="n"/>
+      <c r="G39" s="8" t="n"/>
+      <c r="H39" s="8" t="n"/>
+      <c r="I39" s="8" t="n"/>
+      <c r="J39" s="8" t="n"/>
+      <c r="K39" s="8" t="n"/>
+      <c r="L39" s="8" t="n"/>
+      <c r="M39" s="9" t="n"/>
+      <c r="N39" s="8" t="n"/>
+      <c r="O39" s="14" t="n"/>
+      <c r="P39" s="18" t="n"/>
+      <c r="Q39" s="22" t="n"/>
+      <c r="R39" s="11" t="n"/>
+      <c r="S39" s="11" t="n"/>
+      <c r="T39" s="13" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="n"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="8" t="n"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="8" t="n"/>
+      <c r="J40" s="8" t="n"/>
+      <c r="K40" s="8" t="n"/>
+      <c r="L40" s="8" t="n"/>
+      <c r="M40" s="9" t="n"/>
+      <c r="N40" s="8" t="n"/>
+      <c r="O40" s="14" t="n"/>
+      <c r="P40" s="18" t="n"/>
+      <c r="Q40" s="22" t="n"/>
+      <c r="R40" s="11" t="n"/>
+      <c r="S40" s="11" t="n"/>
+      <c r="T40" s="13" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="n"/>
+      <c r="B41" s="8" t="n"/>
+      <c r="C41" s="8" t="n"/>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="8" t="n"/>
+      <c r="F41" s="8" t="n"/>
+      <c r="G41" s="8" t="n"/>
+      <c r="H41" s="8" t="n"/>
+      <c r="I41" s="8" t="n"/>
+      <c r="J41" s="8" t="n"/>
+      <c r="K41" s="8" t="n"/>
+      <c r="L41" s="8" t="n"/>
+      <c r="M41" s="9" t="n"/>
+      <c r="N41" s="8" t="n"/>
+      <c r="O41" s="14" t="n"/>
+      <c r="P41" s="18" t="n"/>
+      <c r="Q41" s="22" t="n"/>
+      <c r="R41" s="11" t="n"/>
+      <c r="S41" s="11" t="n"/>
+      <c r="T41" s="13" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="n"/>
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="8" t="n"/>
+      <c r="F42" s="8" t="n"/>
+      <c r="G42" s="8" t="n"/>
+      <c r="H42" s="8" t="n"/>
+      <c r="I42" s="8" t="n"/>
+      <c r="J42" s="8" t="n"/>
+      <c r="K42" s="8" t="n"/>
+      <c r="L42" s="8" t="n"/>
+      <c r="M42" s="9" t="n"/>
+      <c r="N42" s="8" t="n"/>
+      <c r="O42" s="14" t="n"/>
+      <c r="P42" s="18" t="n"/>
+      <c r="Q42" s="22" t="n"/>
+      <c r="R42" s="11" t="n"/>
+      <c r="S42" s="11" t="n"/>
+      <c r="T42" s="13" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="n"/>
+      <c r="B43" s="8" t="n"/>
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="8" t="n"/>
+      <c r="F43" s="8" t="n"/>
+      <c r="G43" s="8" t="n"/>
+      <c r="H43" s="8" t="n"/>
+      <c r="I43" s="8" t="n"/>
+      <c r="J43" s="8" t="n"/>
+      <c r="K43" s="8" t="n"/>
+      <c r="L43" s="8" t="n"/>
+      <c r="M43" s="9" t="n"/>
+      <c r="N43" s="8" t="n"/>
+      <c r="O43" s="14" t="n"/>
+      <c r="P43" s="18" t="n"/>
+      <c r="Q43" s="22" t="n"/>
+      <c r="R43" s="11" t="n"/>
+      <c r="S43" s="11" t="n"/>
+      <c r="T43" s="13" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="n"/>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="8" t="n"/>
+      <c r="G44" s="8" t="n"/>
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="8" t="n"/>
+      <c r="J44" s="8" t="n"/>
+      <c r="K44" s="8" t="n"/>
+      <c r="L44" s="8" t="n"/>
+      <c r="M44" s="9" t="n"/>
+      <c r="N44" s="8" t="n"/>
+      <c r="O44" s="14" t="n"/>
+      <c r="P44" s="18" t="n"/>
+      <c r="Q44" s="22" t="n"/>
+      <c r="R44" s="11" t="n"/>
+      <c r="S44" s="11" t="n"/>
+      <c r="T44" s="13" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="n"/>
+      <c r="B45" s="8" t="n"/>
+      <c r="C45" s="8" t="n"/>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="8" t="n"/>
+      <c r="F45" s="8" t="n"/>
+      <c r="G45" s="8" t="n"/>
+      <c r="H45" s="8" t="n"/>
+      <c r="I45" s="8" t="n"/>
+      <c r="J45" s="8" t="n"/>
+      <c r="K45" s="8" t="n"/>
+      <c r="L45" s="8" t="n"/>
+      <c r="M45" s="9" t="n"/>
+      <c r="N45" s="8" t="n"/>
+      <c r="O45" s="14" t="n"/>
+      <c r="P45" s="18" t="n"/>
+      <c r="Q45" s="22" t="n"/>
+      <c r="R45" s="11" t="n"/>
+      <c r="S45" s="11" t="n"/>
+      <c r="T45" s="13" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="n"/>
+      <c r="B46" s="8" t="n"/>
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="8" t="n"/>
+      <c r="E46" s="8" t="n"/>
+      <c r="F46" s="8" t="n"/>
+      <c r="G46" s="8" t="n"/>
+      <c r="H46" s="8" t="n"/>
+      <c r="I46" s="8" t="n"/>
+      <c r="J46" s="8" t="n"/>
+      <c r="K46" s="8" t="n"/>
+      <c r="L46" s="8" t="n"/>
+      <c r="M46" s="9" t="n"/>
+      <c r="N46" s="8" t="n"/>
+      <c r="O46" s="14" t="n"/>
+      <c r="P46" s="18" t="n"/>
+      <c r="Q46" s="22" t="n"/>
+      <c r="R46" s="11" t="n"/>
+      <c r="S46" s="11" t="n"/>
+      <c r="T46" s="13" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="n"/>
+      <c r="B47" s="8" t="n"/>
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="8" t="n"/>
+      <c r="F47" s="8" t="n"/>
+      <c r="G47" s="8" t="n"/>
+      <c r="H47" s="8" t="n"/>
+      <c r="I47" s="8" t="n"/>
+      <c r="J47" s="8" t="n"/>
+      <c r="K47" s="8" t="n"/>
+      <c r="L47" s="8" t="n"/>
+      <c r="M47" s="9" t="n"/>
+      <c r="N47" s="8" t="n"/>
+      <c r="O47" s="14" t="n"/>
+      <c r="P47" s="18" t="n"/>
+      <c r="Q47" s="22" t="n"/>
+      <c r="R47" s="11" t="n"/>
+      <c r="S47" s="11" t="n"/>
+      <c r="T47" s="13" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="n"/>
+      <c r="B48" s="8" t="n"/>
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="8" t="n"/>
+      <c r="E48" s="8" t="n"/>
+      <c r="F48" s="8" t="n"/>
+      <c r="G48" s="8" t="n"/>
+      <c r="H48" s="8" t="n"/>
+      <c r="I48" s="8" t="n"/>
+      <c r="J48" s="8" t="n"/>
+      <c r="K48" s="8" t="n"/>
+      <c r="L48" s="8" t="n"/>
+      <c r="M48" s="9" t="n"/>
+      <c r="N48" s="8" t="n"/>
+      <c r="O48" s="14" t="n"/>
+      <c r="P48" s="18" t="n"/>
+      <c r="Q48" s="22" t="n"/>
+      <c r="R48" s="11" t="n"/>
+      <c r="S48" s="11" t="n"/>
+      <c r="T48" s="13" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="n"/>
+      <c r="B49" s="8" t="n"/>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="8" t="n"/>
+      <c r="E49" s="8" t="n"/>
+      <c r="F49" s="8" t="n"/>
+      <c r="G49" s="8" t="n"/>
+      <c r="H49" s="8" t="n"/>
+      <c r="I49" s="8" t="n"/>
+      <c r="J49" s="8" t="n"/>
+      <c r="K49" s="8" t="n"/>
+      <c r="L49" s="8" t="n"/>
+      <c r="M49" s="9" t="n"/>
+      <c r="N49" s="8" t="n"/>
+      <c r="O49" s="14" t="n"/>
+      <c r="P49" s="18" t="n"/>
+      <c r="Q49" s="22" t="n"/>
+      <c r="R49" s="11" t="n"/>
+      <c r="S49" s="11" t="n"/>
+      <c r="T49" s="13" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="n"/>
+      <c r="B50" s="8" t="n"/>
+      <c r="C50" s="8" t="n"/>
+      <c r="D50" s="8" t="n"/>
+      <c r="E50" s="8" t="n"/>
+      <c r="F50" s="8" t="n"/>
+      <c r="G50" s="8" t="n"/>
+      <c r="H50" s="8" t="n"/>
+      <c r="I50" s="8" t="n"/>
+      <c r="J50" s="8" t="n"/>
+      <c r="K50" s="8" t="n"/>
+      <c r="L50" s="8" t="n"/>
+      <c r="M50" s="9" t="n"/>
+      <c r="N50" s="8" t="n"/>
+      <c r="O50" s="14" t="n"/>
+      <c r="P50" s="18" t="n"/>
+      <c r="Q50" s="22" t="n"/>
+      <c r="R50" s="11" t="n"/>
+      <c r="S50" s="11" t="n"/>
+      <c r="T50" s="13" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="n"/>
+      <c r="B51" s="8" t="n"/>
+      <c r="C51" s="8" t="n"/>
+      <c r="D51" s="8" t="n"/>
+      <c r="E51" s="8" t="n"/>
+      <c r="F51" s="8" t="n"/>
+      <c r="G51" s="8" t="n"/>
+      <c r="H51" s="8" t="n"/>
+      <c r="I51" s="8" t="n"/>
+      <c r="J51" s="8" t="n"/>
+      <c r="K51" s="8" t="n"/>
+      <c r="L51" s="8" t="n"/>
+      <c r="M51" s="9" t="n"/>
+      <c r="N51" s="8" t="n"/>
+      <c r="O51" s="14" t="n"/>
+      <c r="P51" s="18" t="n"/>
+      <c r="Q51" s="22" t="n"/>
+      <c r="R51" s="11" t="n"/>
+      <c r="S51" s="11" t="n"/>
+      <c r="T51" s="13" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="n"/>
+      <c r="B52" s="8" t="n"/>
+      <c r="C52" s="8" t="n"/>
+      <c r="D52" s="8" t="n"/>
+      <c r="E52" s="8" t="n"/>
+      <c r="F52" s="8" t="n"/>
+      <c r="G52" s="8" t="n"/>
+      <c r="H52" s="8" t="n"/>
+      <c r="I52" s="8" t="n"/>
+      <c r="J52" s="8" t="n"/>
+      <c r="K52" s="8" t="n"/>
+      <c r="L52" s="8" t="n"/>
+      <c r="M52" s="9" t="n"/>
+      <c r="N52" s="8" t="n"/>
+      <c r="O52" s="14" t="n"/>
+      <c r="P52" s="18" t="n"/>
+      <c r="Q52" s="22" t="n"/>
+      <c r="R52" s="11" t="n"/>
+      <c r="S52" s="11" t="n"/>
+      <c r="T52" s="13" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="n"/>
+      <c r="B53" s="8" t="n"/>
+      <c r="C53" s="8" t="n"/>
+      <c r="D53" s="8" t="n"/>
+      <c r="E53" s="8" t="n"/>
+      <c r="F53" s="8" t="n"/>
+      <c r="G53" s="8" t="n"/>
+      <c r="H53" s="8" t="n"/>
+      <c r="I53" s="8" t="n"/>
+      <c r="J53" s="8" t="n"/>
+      <c r="K53" s="8" t="n"/>
+      <c r="L53" s="8" t="n"/>
+      <c r="M53" s="9" t="n"/>
+      <c r="N53" s="8" t="n"/>
+      <c r="O53" s="14" t="n"/>
+      <c r="P53" s="18" t="n"/>
+      <c r="Q53" s="22" t="n"/>
+      <c r="R53" s="11" t="n"/>
+      <c r="S53" s="11" t="n"/>
+      <c r="T53" s="13" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="n"/>
+      <c r="B54" s="8" t="n"/>
+      <c r="C54" s="8" t="n"/>
+      <c r="D54" s="8" t="n"/>
+      <c r="E54" s="8" t="n"/>
+      <c r="F54" s="8" t="n"/>
+      <c r="G54" s="8" t="n"/>
+      <c r="H54" s="8" t="n"/>
+      <c r="I54" s="8" t="n"/>
+      <c r="J54" s="8" t="n"/>
+      <c r="K54" s="8" t="n"/>
+      <c r="L54" s="8" t="n"/>
+      <c r="M54" s="9" t="n"/>
+      <c r="N54" s="8" t="n"/>
+      <c r="O54" s="14" t="n"/>
+      <c r="P54" s="18" t="n"/>
+      <c r="Q54" s="22" t="n"/>
+      <c r="R54" s="11" t="n"/>
+      <c r="S54" s="11" t="n"/>
+      <c r="T54" s="13" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="n"/>
+      <c r="B55" s="8" t="n"/>
+      <c r="C55" s="8" t="n"/>
+      <c r="D55" s="8" t="n"/>
+      <c r="E55" s="8" t="n"/>
+      <c r="F55" s="8" t="n"/>
+      <c r="G55" s="8" t="n"/>
+      <c r="H55" s="8" t="n"/>
+      <c r="I55" s="8" t="n"/>
+      <c r="J55" s="8" t="n"/>
+      <c r="K55" s="8" t="n"/>
+      <c r="L55" s="8" t="n"/>
+      <c r="M55" s="9" t="n"/>
+      <c r="N55" s="8" t="n"/>
+      <c r="O55" s="14" t="n"/>
+      <c r="P55" s="18" t="n"/>
+      <c r="Q55" s="22" t="n"/>
+      <c r="R55" s="11" t="n"/>
+      <c r="S55" s="11" t="n"/>
+      <c r="T55" s="13" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="n"/>
+      <c r="B56" s="8" t="n"/>
+      <c r="C56" s="8" t="n"/>
+      <c r="D56" s="8" t="n"/>
+      <c r="E56" s="8" t="n"/>
+      <c r="F56" s="8" t="n"/>
+      <c r="G56" s="8" t="n"/>
+      <c r="H56" s="8" t="n"/>
+      <c r="I56" s="8" t="n"/>
+      <c r="J56" s="8" t="n"/>
+      <c r="K56" s="8" t="n"/>
+      <c r="L56" s="8" t="n"/>
+      <c r="M56" s="9" t="n"/>
+      <c r="N56" s="8" t="n"/>
+      <c r="O56" s="14" t="n"/>
+      <c r="P56" s="18" t="n"/>
+      <c r="Q56" s="22" t="n"/>
+      <c r="R56" s="11" t="n"/>
+      <c r="S56" s="11" t="n"/>
+      <c r="T56" s="13" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="n"/>
+      <c r="B57" s="8" t="n"/>
+      <c r="C57" s="8" t="n"/>
+      <c r="D57" s="8" t="n"/>
+      <c r="E57" s="8" t="n"/>
+      <c r="F57" s="8" t="n"/>
+      <c r="G57" s="8" t="n"/>
+      <c r="H57" s="8" t="n"/>
+      <c r="I57" s="8" t="n"/>
+      <c r="J57" s="8" t="n"/>
+      <c r="K57" s="8" t="n"/>
+      <c r="L57" s="8" t="n"/>
+      <c r="M57" s="9" t="n"/>
+      <c r="N57" s="8" t="n"/>
+      <c r="O57" s="14" t="n"/>
+      <c r="P57" s="18" t="n"/>
+      <c r="Q57" s="22" t="n"/>
+      <c r="R57" s="11" t="n"/>
+      <c r="S57" s="11" t="n"/>
+      <c r="T57" s="13" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="n"/>
+      <c r="B58" s="8" t="n"/>
+      <c r="C58" s="8" t="n"/>
+      <c r="D58" s="8" t="n"/>
+      <c r="E58" s="8" t="n"/>
+      <c r="F58" s="8" t="n"/>
+      <c r="G58" s="8" t="n"/>
+      <c r="H58" s="8" t="n"/>
+      <c r="I58" s="8" t="n"/>
+      <c r="J58" s="8" t="n"/>
+      <c r="K58" s="8" t="n"/>
+      <c r="L58" s="8" t="n"/>
+      <c r="M58" s="9" t="n"/>
+      <c r="N58" s="8" t="n"/>
+      <c r="O58" s="14" t="n"/>
+      <c r="P58" s="18" t="n"/>
+      <c r="Q58" s="22" t="n"/>
+      <c r="R58" s="11" t="n"/>
+      <c r="S58" s="11" t="n"/>
+      <c r="T58" s="13" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="n"/>
+      <c r="B59" s="8" t="n"/>
+      <c r="C59" s="8" t="n"/>
+      <c r="D59" s="8" t="n"/>
+      <c r="E59" s="8" t="n"/>
+      <c r="F59" s="8" t="n"/>
+      <c r="G59" s="8" t="n"/>
+      <c r="H59" s="8" t="n"/>
+      <c r="I59" s="8" t="n"/>
+      <c r="J59" s="8" t="n"/>
+      <c r="K59" s="8" t="n"/>
+      <c r="L59" s="8" t="n"/>
+      <c r="M59" s="9" t="n"/>
+      <c r="N59" s="8" t="n"/>
+      <c r="O59" s="14" t="n"/>
+      <c r="P59" s="18" t="n"/>
+      <c r="Q59" s="22" t="n"/>
+      <c r="R59" s="11" t="n"/>
+      <c r="S59" s="11" t="n"/>
+      <c r="T59" s="13" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="n"/>
+      <c r="B60" s="8" t="n"/>
+      <c r="C60" s="8" t="n"/>
+      <c r="D60" s="8" t="n"/>
+      <c r="E60" s="8" t="n"/>
+      <c r="F60" s="8" t="n"/>
+      <c r="G60" s="8" t="n"/>
+      <c r="H60" s="8" t="n"/>
+      <c r="I60" s="8" t="n"/>
+      <c r="J60" s="8" t="n"/>
+      <c r="K60" s="8" t="n"/>
+      <c r="L60" s="8" t="n"/>
+      <c r="M60" s="9" t="n"/>
+      <c r="N60" s="8" t="n"/>
+      <c r="O60" s="14" t="n"/>
+      <c r="P60" s="18" t="n"/>
+      <c r="Q60" s="22" t="n"/>
+      <c r="R60" s="11" t="n"/>
+      <c r="S60" s="11" t="n"/>
+      <c r="T60" s="13" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
